--- a/diseases/d105/2026-2029.xlsx
+++ b/diseases/d105/2026-2029.xlsx
@@ -39978,12 +39978,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -40017,13 +40017,13 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>4</v>
+        <v>108</v>
       </c>
       <c r="O221" t="n">
-        <v>4</v>
+        <v>108</v>
       </c>
       <c r="R221" t="n">
-        <v>0.01738276978574758</v>
+        <v>1.009247086254601</v>
       </c>
       <c r="S221" t="inlineStr">
         <is>
@@ -40032,7 +40032,7 @@
       </c>
       <c r="U221" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -40042,70 +40042,75 @@
       </c>
       <c r="AO221" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP221" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ221" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR221" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS221" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
       <c r="AT221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV221" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA221" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB221" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC221" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -40137,12 +40142,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -40176,29 +40181,29 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>4</v>
+        <v>108</v>
       </c>
       <c r="O222" t="n">
-        <v>4</v>
+        <v>108</v>
       </c>
       <c r="U222" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
       <c r="V222" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
       <c r="W222" t="inlineStr">
         <is>
-          <t>SRC_TW_NIDSS</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X222" t="inlineStr">
         <is>
-          <t>桿菌性痢疾</t>
+          <t>Shigellainfektion</t>
         </is>
       </c>
       <c r="Y222" t="inlineStr">
@@ -40208,7 +40213,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -40223,7 +40228,7 @@
       </c>
       <c r="AC222" t="inlineStr">
         <is>
-          <t>country:TW:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD222" t="inlineStr">
@@ -40258,17 +40263,17 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>TW_NIDSS_004_current</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
         <is>
-          <t>Taiwan NIDSS disease code 004, bacillary dysentery caused by Shigella; distinct from amoebiasis.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
         </is>
       </c>
       <c r="AM222" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN222" t="b">
@@ -40276,70 +40281,75 @@
       </c>
       <c r="AO222" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ222" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR222" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS222" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
       <c r="AT222" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA222" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -40371,12 +40381,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -40410,81 +40420,95 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>226</v>
+        <v>4</v>
       </c>
       <c r="O223" t="n">
-        <v>226</v>
+        <v>4</v>
       </c>
       <c r="R223" t="n">
-        <v>0.0647498618005881</v>
+        <v>0.01738276978574758</v>
       </c>
       <c r="S223" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>SER_TW_SHIGELLOSIS_004</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO223" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR223" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS223" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ223" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS223" t="inlineStr">
+        <is>
+          <t>SER_TW_SHIGELLOSIS_004</t>
+        </is>
+      </c>
       <c r="AT223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA223" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -40511,17 +40535,17 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -40546,7 +40570,7 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
@@ -40555,35 +40579,107 @@
         </is>
       </c>
       <c r="N224" t="n">
+        <v>4</v>
+      </c>
+      <c r="O224" t="n">
+        <v>4</v>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>SER_TW_SHIGELLOSIS_004</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>SER_TW_SHIGELLOSIS_004</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X224" t="inlineStr">
+        <is>
+          <t>桿菌性痢疾</t>
+        </is>
+      </c>
+      <c r="Y224" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z224" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB224" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD224" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE224" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF224" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG224" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH224" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI224" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ224" t="inlineStr">
+        <is>
+          <t>TW_NIDSS_004_current</t>
+        </is>
+      </c>
+      <c r="AK224" t="inlineStr">
+        <is>
+          <t>Taiwan NIDSS disease code 004, bacillary dysentery caused by Shigella; distinct from amoebiasis.</t>
+        </is>
+      </c>
+      <c r="AM224" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN224" t="b">
         <v>1</v>
       </c>
-      <c r="O224" t="n">
-        <v>1</v>
-      </c>
-      <c r="P224" t="n">
-        <v>1</v>
-      </c>
-      <c r="R224" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S224" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U224" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA224" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO224" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP224" t="inlineStr">
@@ -40593,12 +40689,12 @@
       </c>
       <c r="AQ224" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS224" t="inlineStr">
         <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+          <t>SER_TW_SHIGELLOSIS_004</t>
         </is>
       </c>
       <c r="AT224" t="n">
@@ -40606,47 +40702,47 @@
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -40673,17 +40769,17 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -40708,7 +40804,7 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
@@ -40717,173 +40813,81 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>1</v>
+        <v>226</v>
       </c>
       <c r="O225" t="n">
-        <v>1</v>
-      </c>
-      <c r="P225" t="n">
-        <v>1</v>
-      </c>
-      <c r="U225" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V225" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W225" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X225" t="inlineStr">
-        <is>
-          <t>Bacterial dysentery</t>
-        </is>
-      </c>
-      <c r="Y225" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z225" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA225" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB225" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC225" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD225" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE225" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF225" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG225" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH225" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI225" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ225" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK225" t="inlineStr">
-        <is>
-          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
-        </is>
-      </c>
-      <c r="AM225" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN225" t="b">
-        <v>1</v>
+        <v>226</v>
+      </c>
+      <c r="R225" t="n">
+        <v>0.0647498618005881</v>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO225" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ225" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS225" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR225" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS225" t="inlineStr"/>
       <c r="AT225" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB225" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC225" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -40915,12 +40919,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -40945,7 +40949,7 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
@@ -40954,81 +40958,98 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>232</v>
+        <v>1</v>
       </c>
       <c r="O226" t="n">
-        <v>232</v>
+        <v>1</v>
+      </c>
+      <c r="P226" t="n">
+        <v>1</v>
       </c>
       <c r="R226" t="n">
-        <v>0.06646888468024974</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S226" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO226" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR226" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS226" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ226" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS226" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -41055,7 +41076,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -41090,7 +41111,7 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
@@ -41107,23 +41128,98 @@
       <c r="P227" t="n">
         <v>1</v>
       </c>
-      <c r="R227" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S227" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U227" t="inlineStr">
         <is>
           <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
         </is>
       </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W227" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X227" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y227" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z227" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA227" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB227" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC227" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD227" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE227" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF227" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG227" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH227" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI227" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ227" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK227" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM227" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN227" t="b">
+        <v>1</v>
       </c>
       <c r="AO227" t="inlineStr">
         <is>
@@ -41217,17 +41313,17 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -41252,7 +41348,7 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
@@ -41261,173 +41357,81 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>1</v>
+        <v>232</v>
       </c>
       <c r="O228" t="n">
-        <v>1</v>
-      </c>
-      <c r="P228" t="n">
-        <v>1</v>
-      </c>
-      <c r="U228" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V228" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W228" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X228" t="inlineStr">
-        <is>
-          <t>Bacterial dysentery</t>
-        </is>
-      </c>
-      <c r="Y228" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z228" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA228" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB228" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC228" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD228" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE228" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF228" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG228" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH228" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI228" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ228" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK228" t="inlineStr">
-        <is>
-          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
-        </is>
-      </c>
-      <c r="AM228" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN228" t="b">
-        <v>1</v>
+        <v>232</v>
+      </c>
+      <c r="R228" t="n">
+        <v>0.06646888468024974</v>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO228" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ228" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS228" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR228" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS228" t="inlineStr"/>
       <c r="AT228" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB228" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC228" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -41459,12 +41463,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -41489,7 +41493,7 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
@@ -41498,81 +41502,98 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>225</v>
+        <v>1</v>
       </c>
       <c r="O229" t="n">
-        <v>225</v>
+        <v>1</v>
+      </c>
+      <c r="P229" t="n">
+        <v>1</v>
       </c>
       <c r="R229" t="n">
-        <v>0.06446335798731118</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S229" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO229" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR229" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS229" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ229" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS229" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV229" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA229" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB229" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC229" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -41599,7 +41620,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -41634,7 +41655,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
@@ -41643,31 +41664,106 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O230" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P230" t="n">
-        <v>4</v>
-      </c>
-      <c r="R230" t="n">
-        <v>0.003267233630263065</v>
-      </c>
-      <c r="S230" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U230" t="inlineStr">
         <is>
           <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
         </is>
       </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X230" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y230" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z230" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA230" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB230" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC230" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD230" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE230" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF230" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG230" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH230" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI230" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ230" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK230" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM230" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN230" t="b">
+        <v>1</v>
       </c>
       <c r="AO230" t="inlineStr">
         <is>
@@ -41761,17 +41857,17 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -41796,7 +41892,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
@@ -41805,173 +41901,81 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>4</v>
+        <v>225</v>
       </c>
       <c r="O231" t="n">
-        <v>4</v>
-      </c>
-      <c r="P231" t="n">
-        <v>4</v>
-      </c>
-      <c r="U231" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V231" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W231" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X231" t="inlineStr">
-        <is>
-          <t>Bacterial dysentery</t>
-        </is>
-      </c>
-      <c r="Y231" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z231" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA231" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB231" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC231" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD231" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE231" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF231" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG231" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH231" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI231" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ231" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK231" t="inlineStr">
-        <is>
-          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
-        </is>
-      </c>
-      <c r="AM231" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN231" t="b">
-        <v>1</v>
+        <v>225</v>
+      </c>
+      <c r="R231" t="n">
+        <v>0.06446335798731118</v>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO231" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ231" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS231" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR231" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS231" t="inlineStr"/>
       <c r="AT231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -42003,12 +42007,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -42033,7 +42037,7 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
@@ -42042,81 +42046,98 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>214</v>
+        <v>4</v>
       </c>
       <c r="O232" t="n">
-        <v>214</v>
+        <v>4</v>
+      </c>
+      <c r="P232" t="n">
+        <v>4</v>
       </c>
       <c r="R232" t="n">
-        <v>0.06131181604126484</v>
+        <v>0.003267233630263065</v>
       </c>
       <c r="S232" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO232" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP232" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR232" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS232" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ232" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS232" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV232" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA232" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB232" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC232" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -42143,7 +42164,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -42178,7 +42199,7 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
@@ -42187,31 +42208,106 @@
         </is>
       </c>
       <c r="N233" t="n">
+        <v>4</v>
+      </c>
+      <c r="O233" t="n">
+        <v>4</v>
+      </c>
+      <c r="P233" t="n">
+        <v>4</v>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X233" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y233" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z233" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB233" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD233" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE233" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF233" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG233" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH233" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI233" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ233" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK233" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM233" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN233" t="b">
         <v>1</v>
-      </c>
-      <c r="O233" t="n">
-        <v>1</v>
-      </c>
-      <c r="P233" t="n">
-        <v>1</v>
-      </c>
-      <c r="R233" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S233" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U233" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA233" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
       </c>
       <c r="AO233" t="inlineStr">
         <is>
@@ -42305,17 +42401,17 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -42340,7 +42436,7 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
@@ -42349,173 +42445,81 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>1</v>
+        <v>214</v>
       </c>
       <c r="O234" t="n">
-        <v>1</v>
-      </c>
-      <c r="P234" t="n">
-        <v>1</v>
-      </c>
-      <c r="U234" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V234" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W234" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X234" t="inlineStr">
-        <is>
-          <t>Bacterial dysentery</t>
-        </is>
-      </c>
-      <c r="Y234" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z234" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA234" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB234" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC234" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD234" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE234" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF234" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG234" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH234" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI234" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ234" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK234" t="inlineStr">
-        <is>
-          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
-        </is>
-      </c>
-      <c r="AM234" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN234" t="b">
-        <v>1</v>
+        <v>214</v>
+      </c>
+      <c r="R234" t="n">
+        <v>0.06131181604126484</v>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO234" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ234" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS234" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR234" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS234" t="inlineStr"/>
       <c r="AT234" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA234" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB234" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC234" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -42547,12 +42551,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -42577,7 +42581,7 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
@@ -42586,81 +42590,98 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>208</v>
+        <v>1</v>
       </c>
       <c r="O235" t="n">
-        <v>208</v>
+        <v>1</v>
+      </c>
+      <c r="P235" t="n">
+        <v>1</v>
       </c>
       <c r="R235" t="n">
-        <v>0.05959279316160321</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S235" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO235" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR235" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS235" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ235" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS235" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV235" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA235" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB235" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC235" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -42687,17 +42708,17 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -42722,90 +42743,182 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N236" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O236" t="n">
-        <v>7</v>
-      </c>
-      <c r="R236" t="n">
-        <v>0.02570968273663853</v>
-      </c>
-      <c r="S236" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P236" t="n">
+        <v>1</v>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W236" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X236" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y236" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z236" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB236" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC236" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD236" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE236" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF236" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG236" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH236" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI236" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ236" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK236" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM236" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN236" t="b">
+        <v>1</v>
       </c>
       <c r="AO236" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR236" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS236" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ236" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS236" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV236" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -42837,12 +42950,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -42867,109 +42980,90 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N237" t="n">
+        <v>208</v>
+      </c>
+      <c r="O237" t="n">
+        <v>208</v>
+      </c>
+      <c r="R237" t="n">
+        <v>0.05959279316160321</v>
+      </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO237" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP237" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR237" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS237" t="inlineStr"/>
+      <c r="AT237" t="n">
         <v>0</v>
       </c>
-      <c r="O237" t="n">
-        <v>0</v>
-      </c>
-      <c r="R237" t="n">
-        <v>0</v>
-      </c>
-      <c r="S237" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U237" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1210</t>
-        </is>
-      </c>
-      <c r="AA237" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO237" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP237" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ237" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR237" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS237" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1210</t>
-        </is>
-      </c>
-      <c r="AT237" t="n">
-        <v>2</v>
-      </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -42996,17 +43090,17 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -43040,175 +43134,81 @@
         </is>
       </c>
       <c r="N238" t="n">
+        <v>7</v>
+      </c>
+      <c r="O238" t="n">
+        <v>7</v>
+      </c>
+      <c r="R238" t="n">
+        <v>0.02570968273663853</v>
+      </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO238" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP238" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR238" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS238" t="inlineStr"/>
+      <c r="AT238" t="n">
         <v>0</v>
       </c>
-      <c r="O238" t="n">
-        <v>0</v>
-      </c>
-      <c r="U238" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1210</t>
-        </is>
-      </c>
-      <c r="V238" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1210</t>
-        </is>
-      </c>
-      <c r="W238" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X238" t="inlineStr">
-        <is>
-          <t>Shigella</t>
-        </is>
-      </c>
-      <c r="Y238" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z238" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA238" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB238" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC238" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD238" t="inlineStr">
+      <c r="AU238" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV238" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE238" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF238" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG238" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH238" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI238" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ238" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK238" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1210.</t>
-        </is>
-      </c>
-      <c r="AM238" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN238" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO238" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP238" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ238" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR238" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS238" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1210</t>
-        </is>
-      </c>
-      <c r="AT238" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU238" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV238" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA238" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB238" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC238" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -43240,12 +43240,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -43292,68 +43292,87 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1210</t>
+        </is>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO239" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP239" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ239" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR239" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS239" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS239" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1210</t>
+        </is>
+      </c>
       <c r="AT239" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV239" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA239" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB239" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC239" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -43380,17 +43399,17 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -43429,17 +43448,34 @@
       <c r="O240" t="n">
         <v>0</v>
       </c>
-      <c r="R240" t="n">
-        <v>0</v>
-      </c>
-      <c r="S240" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U240" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1210</t>
+        </is>
+      </c>
+      <c r="V240" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1210</t>
+        </is>
+      </c>
+      <c r="W240" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X240" t="inlineStr">
+        <is>
+          <t>Shigella</t>
+        </is>
+      </c>
+      <c r="Y240" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z240" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
@@ -43447,6 +43483,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB240" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC240" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD240" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE240" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF240" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG240" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH240" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI240" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ240" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK240" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1210.</t>
+        </is>
+      </c>
+      <c r="AM240" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN240" t="b">
+        <v>1</v>
+      </c>
       <c r="AO240" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -43459,7 +43553,7 @@
       </c>
       <c r="AQ240" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR240" t="inlineStr">
@@ -43469,7 +43563,7 @@
       </c>
       <c r="AS240" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1210</t>
         </is>
       </c>
       <c r="AT240" t="n">
@@ -43477,47 +43571,47 @@
       </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV240" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA240" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB240" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC240" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -43544,17 +43638,17 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -43593,168 +43687,477 @@
       <c r="O241" t="n">
         <v>0</v>
       </c>
-      <c r="U241" t="inlineStr">
+      <c r="R241" t="n">
+        <v>0</v>
+      </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO241" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP241" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR241" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS241" t="inlineStr"/>
+      <c r="AT241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU241" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV241" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW241" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX241" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY241" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA241" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB241" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC241" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>shigellosis</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N242" t="n">
+        <v>0</v>
+      </c>
+      <c r="O242" t="n">
+        <v>0</v>
+      </c>
+      <c r="R242" t="n">
+        <v>0</v>
+      </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U242" t="inlineStr">
         <is>
           <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
-      <c r="V241" t="inlineStr">
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO242" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP242" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ242" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR242" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS242" t="inlineStr">
         <is>
           <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
-      <c r="W241" t="inlineStr">
+      <c r="AT242" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU242" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV242" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW242" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX242" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY242" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA242" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB242" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC242" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>shigellosis</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N243" t="n">
+        <v>0</v>
+      </c>
+      <c r="O243" t="n">
+        <v>0</v>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_502_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V243" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_502_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W243" t="inlineStr">
         <is>
           <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
-      <c r="X241" t="inlineStr">
+      <c r="X243" t="inlineStr">
         <is>
           <t>Shigellose</t>
         </is>
       </c>
-      <c r="Y241" t="inlineStr">
+      <c r="Y243" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z241" t="inlineStr">
+      <c r="Z243" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA241" t="inlineStr">
+      <c r="AA243" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB241" t="inlineStr">
+      <c r="AB243" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC241" t="inlineStr">
+      <c r="AC243" t="inlineStr">
         <is>
           <t>country:NO:national</t>
         </is>
       </c>
-      <c r="AD241" t="inlineStr">
+      <c r="AD243" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE241" t="inlineStr">
+      <c r="AE243" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF241" t="inlineStr">
+      <c r="AF243" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG241" t="inlineStr">
+      <c r="AG243" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH241" t="inlineStr">
+      <c r="AH243" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI241" t="inlineStr">
+      <c r="AI243" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ241" t="inlineStr">
+      <c r="AJ243" t="inlineStr">
         <is>
           <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
-      <c r="AK241" t="inlineStr">
+      <c r="AK243" t="inlineStr">
         <is>
           <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
-      <c r="AM241" t="inlineStr">
+      <c r="AM243" t="inlineStr">
         <is>
           <t>provisional; raw; revised</t>
         </is>
       </c>
-      <c r="AN241" t="b">
+      <c r="AN243" t="b">
         <v>1</v>
       </c>
-      <c r="AO241" t="inlineStr">
+      <c r="AO243" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP241" t="inlineStr">
+      <c r="AP243" t="inlineStr">
         <is>
           <t>representative_series</t>
         </is>
       </c>
-      <c r="AQ241" t="inlineStr">
+      <c r="AQ243" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AR241" t="inlineStr">
+      <c r="AR243" t="inlineStr">
         <is>
           <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
-      <c r="AS241" t="inlineStr">
+      <c r="AS243" t="inlineStr">
         <is>
           <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
-      <c r="AT241" t="n">
+      <c r="AT243" t="n">
         <v>2</v>
       </c>
-      <c r="AU241" t="inlineStr">
+      <c r="AU243" t="inlineStr">
         <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV241" t="inlineStr">
+      <c r="AV243" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW241" t="inlineStr">
+      <c r="AW243" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX241" t="inlineStr">
+      <c r="AX243" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY241" t="inlineStr">
+      <c r="AY243" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ241" t="inlineStr">
+      <c r="AZ243" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA241" t="inlineStr">
+      <c r="BA243" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB241" t="inlineStr">
+      <c r="BB243" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC241" t="inlineStr">
+      <c r="BC243" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -43876,7 +44279,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10">
@@ -43886,7 +44289,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11">
@@ -43906,7 +44309,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13">
@@ -43938,7 +44341,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8908</v>
+        <v>9016</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d105/2026-2029.xlsx
+++ b/diseases/d105/2026-2029.xlsx
@@ -38069,13 +38069,13 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="O209" t="n">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="R209" t="n">
-        <v>0.7015070575282799</v>
+        <v>0.7272167402649184</v>
       </c>
       <c r="S209" t="inlineStr">
         <is>
@@ -43095,12 +43095,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -43125,90 +43125,107 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N238" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O238" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="P238" t="n">
+        <v>2</v>
       </c>
       <c r="R238" t="n">
-        <v>0.02570968273663853</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S238" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO238" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP238" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR238" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS238" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ238" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS238" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV238" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA238" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB238" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC238" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -43235,17 +43252,17 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -43270,37 +43287,115 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N239" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O239" t="n">
-        <v>0</v>
-      </c>
-      <c r="R239" t="n">
-        <v>0</v>
-      </c>
-      <c r="S239" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P239" t="n">
+        <v>2</v>
       </c>
       <c r="U239" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1210</t>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V239" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W239" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X239" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y239" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z239" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB239" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC239" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD239" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE239" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF239" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG239" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH239" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI239" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ239" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK239" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM239" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN239" t="b">
+        <v>1</v>
       </c>
       <c r="AO239" t="inlineStr">
         <is>
@@ -43309,70 +43404,65 @@
       </c>
       <c r="AP239" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ239" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR239" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS239" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1210</t>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT239" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV239" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA239" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB239" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC239" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -43399,17 +43489,17 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -43443,175 +43533,81 @@
         </is>
       </c>
       <c r="N240" t="n">
+        <v>7</v>
+      </c>
+      <c r="O240" t="n">
+        <v>7</v>
+      </c>
+      <c r="R240" t="n">
+        <v>0.02570968273663853</v>
+      </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO240" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP240" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR240" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS240" t="inlineStr"/>
+      <c r="AT240" t="n">
         <v>0</v>
       </c>
-      <c r="O240" t="n">
-        <v>0</v>
-      </c>
-      <c r="U240" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1210</t>
-        </is>
-      </c>
-      <c r="V240" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1210</t>
-        </is>
-      </c>
-      <c r="W240" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X240" t="inlineStr">
-        <is>
-          <t>Shigella</t>
-        </is>
-      </c>
-      <c r="Y240" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z240" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA240" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB240" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC240" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD240" t="inlineStr">
+      <c r="AU240" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV240" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE240" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF240" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG240" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH240" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI240" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ240" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK240" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1210.</t>
-        </is>
-      </c>
-      <c r="AM240" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN240" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO240" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP240" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ240" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR240" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS240" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1210</t>
-        </is>
-      </c>
-      <c r="AT240" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU240" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV240" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA240" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB240" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC240" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -43643,12 +43639,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -43695,68 +43691,87 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1210</t>
+        </is>
+      </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO241" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP241" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ241" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR241" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS241" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS241" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1210</t>
+        </is>
+      </c>
       <c r="AT241" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV241" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA241" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB241" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC241" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -43783,17 +43798,17 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -43832,17 +43847,34 @@
       <c r="O242" t="n">
         <v>0</v>
       </c>
-      <c r="R242" t="n">
-        <v>0</v>
-      </c>
-      <c r="S242" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U242" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1210</t>
+        </is>
+      </c>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1210</t>
+        </is>
+      </c>
+      <c r="W242" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X242" t="inlineStr">
+        <is>
+          <t>Shigella</t>
+        </is>
+      </c>
+      <c r="Y242" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z242" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
@@ -43850,6 +43882,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB242" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC242" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD242" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE242" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF242" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG242" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH242" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI242" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ242" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK242" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1210.</t>
+        </is>
+      </c>
+      <c r="AM242" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN242" t="b">
+        <v>1</v>
+      </c>
       <c r="AO242" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -43862,7 +43952,7 @@
       </c>
       <c r="AQ242" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR242" t="inlineStr">
@@ -43872,7 +43962,7 @@
       </c>
       <c r="AS242" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1210</t>
         </is>
       </c>
       <c r="AT242" t="n">
@@ -43880,47 +43970,47 @@
       </c>
       <c r="AU242" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV242" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA242" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB242" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC242" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -43947,17 +44037,17 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -43996,168 +44086,477 @@
       <c r="O243" t="n">
         <v>0</v>
       </c>
-      <c r="U243" t="inlineStr">
+      <c r="R243" t="n">
+        <v>0</v>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO243" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP243" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR243" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS243" t="inlineStr"/>
+      <c r="AT243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU243" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV243" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW243" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX243" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY243" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA243" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB243" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC243" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>shigellosis</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N244" t="n">
+        <v>0</v>
+      </c>
+      <c r="O244" t="n">
+        <v>0</v>
+      </c>
+      <c r="R244" t="n">
+        <v>0</v>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U244" t="inlineStr">
         <is>
           <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
-      <c r="V243" t="inlineStr">
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO244" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP244" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ244" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR244" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS244" t="inlineStr">
         <is>
           <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
-      <c r="W243" t="inlineStr">
+      <c r="AT244" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU244" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV244" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW244" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX244" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY244" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA244" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB244" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC244" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>shigellosis</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N245" t="n">
+        <v>0</v>
+      </c>
+      <c r="O245" t="n">
+        <v>0</v>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_502_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_502_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W245" t="inlineStr">
         <is>
           <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
-      <c r="X243" t="inlineStr">
+      <c r="X245" t="inlineStr">
         <is>
           <t>Shigellose</t>
         </is>
       </c>
-      <c r="Y243" t="inlineStr">
+      <c r="Y245" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z243" t="inlineStr">
+      <c r="Z245" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA243" t="inlineStr">
+      <c r="AA245" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB243" t="inlineStr">
+      <c r="AB245" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC243" t="inlineStr">
+      <c r="AC245" t="inlineStr">
         <is>
           <t>country:NO:national</t>
         </is>
       </c>
-      <c r="AD243" t="inlineStr">
+      <c r="AD245" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE243" t="inlineStr">
+      <c r="AE245" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF243" t="inlineStr">
+      <c r="AF245" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG243" t="inlineStr">
+      <c r="AG245" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH243" t="inlineStr">
+      <c r="AH245" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI243" t="inlineStr">
+      <c r="AI245" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ243" t="inlineStr">
+      <c r="AJ245" t="inlineStr">
         <is>
           <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
-      <c r="AK243" t="inlineStr">
+      <c r="AK245" t="inlineStr">
         <is>
           <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
-      <c r="AM243" t="inlineStr">
+      <c r="AM245" t="inlineStr">
         <is>
           <t>provisional; raw; revised</t>
         </is>
       </c>
-      <c r="AN243" t="b">
+      <c r="AN245" t="b">
         <v>1</v>
       </c>
-      <c r="AO243" t="inlineStr">
+      <c r="AO245" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP243" t="inlineStr">
+      <c r="AP245" t="inlineStr">
         <is>
           <t>representative_series</t>
         </is>
       </c>
-      <c r="AQ243" t="inlineStr">
+      <c r="AQ245" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AR243" t="inlineStr">
+      <c r="AR245" t="inlineStr">
         <is>
           <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
-      <c r="AS243" t="inlineStr">
+      <c r="AS245" t="inlineStr">
         <is>
           <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
-      <c r="AT243" t="n">
+      <c r="AT245" t="n">
         <v>2</v>
       </c>
-      <c r="AU243" t="inlineStr">
+      <c r="AU245" t="inlineStr">
         <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV243" t="inlineStr">
+      <c r="AV245" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW243" t="inlineStr">
+      <c r="AW245" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX243" t="inlineStr">
+      <c r="AX245" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY243" t="inlineStr">
+      <c r="AY245" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ243" t="inlineStr">
+      <c r="AZ245" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA243" t="inlineStr">
+      <c r="BA245" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB243" t="inlineStr">
+      <c r="BB245" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC243" t="inlineStr">
+      <c r="BC245" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -44279,7 +44678,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10">
@@ -44289,7 +44688,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -44309,7 +44708,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13">
@@ -44341,7 +44740,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9016</v>
+        <v>9025</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d105/2026-2029.xlsx
+++ b/diseases/d105/2026-2029.xlsx
@@ -38069,13 +38069,13 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O209" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="R209" t="n">
-        <v>0.7272167402649184</v>
+        <v>0.7308895520844382</v>
       </c>
       <c r="S209" t="inlineStr">
         <is>
@@ -39614,13 +39614,13 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O219" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R219" t="n">
-        <v>0.1592078243215956</v>
+        <v>0.1945873408375057</v>
       </c>
       <c r="S219" t="inlineStr">
         <is>
@@ -39778,10 +39778,10 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O220" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="U220" t="inlineStr">
         <is>
@@ -44226,13 +44226,13 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O244" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R244" t="n">
-        <v>0</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S244" t="inlineStr">
         <is>
@@ -44390,10 +44390,10 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U245" t="inlineStr">
         <is>
@@ -44740,7 +44740,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9025</v>
+        <v>9029</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d105/2026-2029.xlsx
+++ b/diseases/d105/2026-2029.xlsx
@@ -38069,13 +38069,13 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="O209" t="n">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="R209" t="n">
-        <v>0.7308895520844382</v>
+        <v>0.7492536111820371</v>
       </c>
       <c r="S209" t="inlineStr">
         <is>
@@ -44559,6 +44559,151 @@
       <c r="BC245" t="inlineStr">
         <is>
           <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>shigellosis</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N246" t="n">
+        <v>198</v>
+      </c>
+      <c r="O246" t="n">
+        <v>198</v>
+      </c>
+      <c r="R246" t="n">
+        <v>0.05672775502883383</v>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO246" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP246" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR246" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS246" t="inlineStr"/>
+      <c r="AT246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU246" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV246" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW246" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX246" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY246" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA246" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB246" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC246" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -44595,7 +44740,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -44678,7 +44823,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10">
@@ -44688,7 +44833,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -44740,7 +44885,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9029</v>
+        <v>9232</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d105/2026-2029.xlsx
+++ b/diseases/d105/2026-2029.xlsx
@@ -21155,10 +21155,10 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O114" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -21311,10 +21311,10 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O115" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="U115" t="inlineStr">
         <is>
@@ -27328,10 +27328,10 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O149" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
@@ -27484,10 +27484,10 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O150" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="U150" t="inlineStr">
         <is>
@@ -33424,12 +33424,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -33463,81 +33463,92 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O184" t="n">
-        <v>22</v>
-      </c>
-      <c r="R184" t="n">
-        <v>0.2442328302655099</v>
+        <v>23</v>
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_SHIGELLOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR184" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS184" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ184" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS184" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_SHIGELLOSIS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA184" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB184" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC184" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -33564,17 +33575,17 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -33608,22 +33619,39 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="O185" t="n">
-        <v>2</v>
-      </c>
-      <c r="R185" t="n">
-        <v>0.03557618341728275</v>
-      </c>
-      <c r="S185" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>23</v>
       </c>
       <c r="U185" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1210</t>
+          <t>SER_CA_ON_PHO_IDTO_SHIGELLOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_SHIGELLOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X185" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -33631,6 +33659,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD185" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE185" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF185" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG185" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH185" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI185" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ185" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK185" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary shigellosis notifications; confirmed cases only under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM185" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN185" t="b">
+        <v>1</v>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -33638,70 +33724,65 @@
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ185" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR185" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS185" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1210</t>
+          <t>SER_CA_ON_PHO_IDTO_SHIGELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT185" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV185" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA185" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB185" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC185" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -33728,17 +33809,17 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -33772,175 +33853,81 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="O186" t="n">
-        <v>2</v>
-      </c>
-      <c r="U186" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1210</t>
-        </is>
-      </c>
-      <c r="V186" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1210</t>
-        </is>
-      </c>
-      <c r="W186" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X186" t="inlineStr">
-        <is>
-          <t>Shigella</t>
-        </is>
-      </c>
-      <c r="Y186" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z186" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA186" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB186" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC186" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD186" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE186" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF186" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG186" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH186" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI186" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ186" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK186" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1210.</t>
-        </is>
-      </c>
-      <c r="AM186" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN186" t="b">
-        <v>1</v>
+        <v>23</v>
+      </c>
+      <c r="R186" t="n">
+        <v>0.2553343225503059</v>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO186" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ186" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR186" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS186" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1210</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS186" t="inlineStr"/>
       <c r="AT186" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA186" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB186" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC186" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -33972,12 +33959,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -34011,81 +33998,100 @@
         </is>
       </c>
       <c r="N187" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O187" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R187" t="n">
-        <v>0.01355270280196709</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="S187" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1210</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ187" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR187" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS187" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS187" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1210</t>
+        </is>
+      </c>
       <c r="AT187" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA187" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB187" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC187" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -34112,17 +34118,17 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -34156,81 +34162,175 @@
         </is>
       </c>
       <c r="N188" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O188" t="n">
-        <v>4</v>
-      </c>
-      <c r="R188" t="n">
-        <v>0.007751879695168184</v>
-      </c>
-      <c r="S188" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1210</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1210</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X188" t="inlineStr">
+        <is>
+          <t>Shigella</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD188" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE188" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF188" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG188" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH188" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI188" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ188" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK188" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1210.</t>
+        </is>
+      </c>
+      <c r="AM188" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN188" t="b">
+        <v>1</v>
       </c>
       <c r="AO188" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP188" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ188" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR188" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS188" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS188" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1210</t>
+        </is>
+      </c>
       <c r="AT188" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU188" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV188" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA188" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB188" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC188" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -34262,12 +34362,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -34301,100 +34401,81 @@
         </is>
       </c>
       <c r="N189" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="O189" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="R189" t="n">
-        <v>0.3184156486431911</v>
+        <v>0.01355270280196709</v>
       </c>
       <c r="S189" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U189" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA189" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO189" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ189" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR189" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS189" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS189" t="inlineStr"/>
       <c r="AT189" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV189" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA189" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB189" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC189" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -34421,17 +34502,17 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -34465,175 +34546,81 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="O190" t="n">
-        <v>18</v>
-      </c>
-      <c r="U190" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V190" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W190" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X190" t="inlineStr">
-        <is>
-          <t>Shigellose</t>
-        </is>
-      </c>
-      <c r="Y190" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z190" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA190" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB190" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD190" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE190" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF190" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG190" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH190" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI190" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ190" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK190" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM190" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN190" t="b">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="R190" t="n">
+        <v>0.007751879695168184</v>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO190" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ190" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR190" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS190" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr"/>
       <c r="AT190" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA190" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -34665,12 +34652,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -34704,13 +34691,13 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="O191" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="R191" t="n">
-        <v>0.1891260466471829</v>
+        <v>0.3184156486431911</v>
       </c>
       <c r="S191" t="inlineStr">
         <is>
@@ -34719,7 +34706,7 @@
       </c>
       <c r="U191" t="inlineStr">
         <is>
-          <t>SER_NZ_SHIGELLOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -34734,7 +34721,7 @@
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ191" t="inlineStr">
@@ -34742,57 +34729,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR191" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS191" t="inlineStr">
         <is>
-          <t>SER_NZ_SHIGELLOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
       <c r="AT191" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA191" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB191" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC191" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -34824,12 +34816,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -34863,29 +34855,29 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="O192" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="U192" t="inlineStr">
         <is>
-          <t>SER_NZ_SHIGELLOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
       <c r="V192" t="inlineStr">
         <is>
-          <t>SER_NZ_SHIGELLOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
       <c r="W192" t="inlineStr">
         <is>
-          <t>SRC_NZ_PHS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X192" t="inlineStr">
         <is>
-          <t>Shigellosis</t>
+          <t>Shigellose</t>
         </is>
       </c>
       <c r="Y192" t="inlineStr">
@@ -34895,7 +34887,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -34910,7 +34902,7 @@
       </c>
       <c r="AC192" t="inlineStr">
         <is>
-          <t>country:NZ:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD192" t="inlineStr">
@@ -34945,17 +34937,17 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>NZ_PHS_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science monthly shigellosis notifications.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM192" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN192" t="b">
@@ -34968,7 +34960,7 @@
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ192" t="inlineStr">
@@ -34976,57 +34968,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR192" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS192" t="inlineStr">
         <is>
-          <t>SER_NZ_SHIGELLOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
       <c r="AT192" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU192" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA192" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB192" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC192" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -35058,12 +35055,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -35097,13 +35094,13 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>76</v>
+        <v>10</v>
       </c>
       <c r="O193" t="n">
-        <v>76</v>
+        <v>10</v>
       </c>
       <c r="R193" t="n">
-        <v>0.7102109125495343</v>
+        <v>0.1891260466471829</v>
       </c>
       <c r="S193" t="inlineStr">
         <is>
@@ -35112,7 +35109,7 @@
       </c>
       <c r="U193" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
+          <t>SER_NZ_SHIGELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -35127,7 +35124,7 @@
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ193" t="inlineStr">
@@ -35135,62 +35132,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR193" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS193" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
+          <t>SER_NZ_SHIGELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT193" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU193" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA193" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB193" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC193" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35222,12 +35214,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -35261,29 +35253,29 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>76</v>
+        <v>10</v>
       </c>
       <c r="O194" t="n">
-        <v>76</v>
+        <v>10</v>
       </c>
       <c r="U194" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
+          <t>SER_NZ_SHIGELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V194" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
+          <t>SER_NZ_SHIGELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W194" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X194" t="inlineStr">
         <is>
-          <t>Shigellainfektion</t>
+          <t>Shigellosis</t>
         </is>
       </c>
       <c r="Y194" t="inlineStr">
@@ -35293,7 +35285,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -35308,7 +35300,7 @@
       </c>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD194" t="inlineStr">
@@ -35343,17 +35335,17 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>New Zealand PHF Science monthly shigellosis notifications.</t>
         </is>
       </c>
       <c r="AM194" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN194" t="b">
@@ -35366,7 +35358,7 @@
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ194" t="inlineStr">
@@ -35374,62 +35366,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR194" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS194" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
+          <t>SER_NZ_SHIGELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT194" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU194" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV194" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA194" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB194" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC194" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35461,12 +35448,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -35500,13 +35487,13 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="O195" t="n">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="R195" t="n">
-        <v>0.08691384892873792</v>
+        <v>0.7102109125495343</v>
       </c>
       <c r="S195" t="inlineStr">
         <is>
@@ -35515,7 +35502,7 @@
       </c>
       <c r="U195" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -35525,70 +35512,75 @@
       </c>
       <c r="AO195" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ195" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR195" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS195" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
       <c r="AT195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA195" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB195" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC195" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -35620,12 +35612,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -35659,29 +35651,29 @@
         </is>
       </c>
       <c r="N196" t="n">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="O196" t="n">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="U196" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
       <c r="V196" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
       <c r="W196" t="inlineStr">
         <is>
-          <t>SRC_TW_NIDSS</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X196" t="inlineStr">
         <is>
-          <t>桿菌性痢疾</t>
+          <t>Shigellainfektion</t>
         </is>
       </c>
       <c r="Y196" t="inlineStr">
@@ -35691,7 +35683,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -35706,7 +35698,7 @@
       </c>
       <c r="AC196" t="inlineStr">
         <is>
-          <t>country:TW:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD196" t="inlineStr">
@@ -35741,17 +35733,17 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>TW_NIDSS_004_current</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
         <is>
-          <t>Taiwan NIDSS disease code 004, bacillary dysentery caused by Shigella; distinct from amoebiasis.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
         </is>
       </c>
       <c r="AM196" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN196" t="b">
@@ -35759,70 +35751,75 @@
       </c>
       <c r="AO196" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ196" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR196" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS196" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
       <c r="AT196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA196" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB196" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC196" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -35854,12 +35851,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -35884,7 +35881,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
@@ -35893,81 +35890,95 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>136</v>
+        <v>20</v>
       </c>
       <c r="O197" t="n">
-        <v>136</v>
+        <v>20</v>
       </c>
       <c r="R197" t="n">
-        <v>0.03896451860566364</v>
+        <v>0.08691384892873792</v>
       </c>
       <c r="S197" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>SER_TW_SHIGELLOSIS_004</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR197" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS197" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ197" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS197" t="inlineStr">
+        <is>
+          <t>SER_TW_SHIGELLOSIS_004</t>
+        </is>
+      </c>
       <c r="AT197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA197" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB197" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC197" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -35994,17 +36005,17 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -36029,7 +36040,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
@@ -36038,35 +36049,107 @@
         </is>
       </c>
       <c r="N198" t="n">
+        <v>20</v>
+      </c>
+      <c r="O198" t="n">
+        <v>20</v>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>SER_TW_SHIGELLOSIS_004</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>SER_TW_SHIGELLOSIS_004</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X198" t="inlineStr">
+        <is>
+          <t>桿菌性痢疾</t>
+        </is>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB198" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD198" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE198" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF198" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG198" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH198" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI198" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ198" t="inlineStr">
+        <is>
+          <t>TW_NIDSS_004_current</t>
+        </is>
+      </c>
+      <c r="AK198" t="inlineStr">
+        <is>
+          <t>Taiwan NIDSS disease code 004, bacillary dysentery caused by Shigella; distinct from amoebiasis.</t>
+        </is>
+      </c>
+      <c r="AM198" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN198" t="b">
         <v>1</v>
       </c>
-      <c r="O198" t="n">
-        <v>1</v>
-      </c>
-      <c r="P198" t="n">
-        <v>1</v>
-      </c>
-      <c r="R198" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S198" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U198" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA198" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO198" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP198" t="inlineStr">
@@ -36076,12 +36159,12 @@
       </c>
       <c r="AQ198" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS198" t="inlineStr">
         <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+          <t>SER_TW_SHIGELLOSIS_004</t>
         </is>
       </c>
       <c r="AT198" t="n">
@@ -36089,47 +36172,47 @@
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC198" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -36156,17 +36239,17 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -36191,7 +36274,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -36200,173 +36283,81 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>1</v>
+        <v>136</v>
       </c>
       <c r="O199" t="n">
-        <v>1</v>
-      </c>
-      <c r="P199" t="n">
-        <v>1</v>
-      </c>
-      <c r="U199" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V199" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W199" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X199" t="inlineStr">
-        <is>
-          <t>Bacterial dysentery</t>
-        </is>
-      </c>
-      <c r="Y199" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z199" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA199" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB199" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC199" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD199" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE199" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF199" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG199" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH199" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI199" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ199" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK199" t="inlineStr">
-        <is>
-          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
-        </is>
-      </c>
-      <c r="AM199" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN199" t="b">
-        <v>1</v>
+        <v>136</v>
+      </c>
+      <c r="R199" t="n">
+        <v>0.03896451860566364</v>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO199" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ199" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS199" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR199" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS199" t="inlineStr"/>
       <c r="AT199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -36398,12 +36389,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -36428,7 +36419,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -36437,81 +36428,98 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>165</v>
+        <v>1</v>
       </c>
       <c r="O200" t="n">
-        <v>165</v>
+        <v>1</v>
+      </c>
+      <c r="P200" t="n">
+        <v>1</v>
       </c>
       <c r="R200" t="n">
-        <v>0.04727312919069485</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S200" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR200" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS200" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ200" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS200" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC200" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36538,7 +36546,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -36573,7 +36581,7 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
@@ -36582,31 +36590,106 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P201" t="n">
-        <v>0</v>
-      </c>
-      <c r="R201" t="n">
-        <v>0</v>
-      </c>
-      <c r="S201" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U201" t="inlineStr">
         <is>
           <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
         </is>
       </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X201" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA201" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD201" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE201" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF201" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG201" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH201" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI201" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ201" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK201" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM201" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN201" t="b">
+        <v>1</v>
       </c>
       <c r="AO201" t="inlineStr">
         <is>
@@ -36700,17 +36783,17 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -36735,7 +36818,7 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
@@ -36744,173 +36827,81 @@
         </is>
       </c>
       <c r="N202" t="n">
+        <v>165</v>
+      </c>
+      <c r="O202" t="n">
+        <v>165</v>
+      </c>
+      <c r="R202" t="n">
+        <v>0.04727312919069485</v>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO202" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP202" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR202" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS202" t="inlineStr"/>
+      <c r="AT202" t="n">
         <v>0</v>
       </c>
-      <c r="O202" t="n">
-        <v>0</v>
-      </c>
-      <c r="P202" t="n">
-        <v>0</v>
-      </c>
-      <c r="U202" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V202" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W202" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X202" t="inlineStr">
-        <is>
-          <t>Bacterial dysentery</t>
-        </is>
-      </c>
-      <c r="Y202" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z202" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA202" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB202" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD202" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE202" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF202" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG202" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH202" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI202" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ202" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK202" t="inlineStr">
-        <is>
-          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
-        </is>
-      </c>
-      <c r="AM202" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN202" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO202" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP202" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ202" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS202" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT202" t="n">
-        <v>1</v>
-      </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV202" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA202" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB202" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC202" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -36942,12 +36933,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -36972,7 +36963,7 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
@@ -36981,81 +36972,98 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="O203" t="n">
-        <v>224</v>
+        <v>0</v>
+      </c>
+      <c r="P203" t="n">
+        <v>0</v>
       </c>
       <c r="R203" t="n">
-        <v>0.06417685417403424</v>
+        <v>0</v>
       </c>
       <c r="S203" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR203" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS203" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ203" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS203" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV203" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA203" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB203" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC203" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37082,7 +37090,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -37117,7 +37125,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
@@ -37126,31 +37134,106 @@
         </is>
       </c>
       <c r="N204" t="n">
+        <v>0</v>
+      </c>
+      <c r="O204" t="n">
+        <v>0</v>
+      </c>
+      <c r="P204" t="n">
+        <v>0</v>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X204" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB204" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD204" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE204" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF204" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG204" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH204" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI204" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ204" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK204" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM204" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN204" t="b">
         <v>1</v>
-      </c>
-      <c r="O204" t="n">
-        <v>1</v>
-      </c>
-      <c r="P204" t="n">
-        <v>1</v>
-      </c>
-      <c r="R204" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S204" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U204" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA204" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
       </c>
       <c r="AO204" t="inlineStr">
         <is>
@@ -37244,17 +37327,17 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -37279,7 +37362,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
@@ -37288,173 +37371,81 @@
         </is>
       </c>
       <c r="N205" t="n">
-        <v>1</v>
+        <v>224</v>
       </c>
       <c r="O205" t="n">
-        <v>1</v>
-      </c>
-      <c r="P205" t="n">
-        <v>1</v>
-      </c>
-      <c r="U205" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V205" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W205" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X205" t="inlineStr">
-        <is>
-          <t>Bacterial dysentery</t>
-        </is>
-      </c>
-      <c r="Y205" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z205" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA205" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB205" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC205" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD205" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE205" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF205" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG205" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH205" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI205" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ205" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK205" t="inlineStr">
-        <is>
-          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
-        </is>
-      </c>
-      <c r="AM205" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN205" t="b">
-        <v>1</v>
+        <v>224</v>
+      </c>
+      <c r="R205" t="n">
+        <v>0.06417685417403424</v>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO205" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ205" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS205" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR205" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS205" t="inlineStr"/>
       <c r="AT205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA205" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB205" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC205" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -37486,12 +37477,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -37516,7 +37507,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
@@ -37525,81 +37516,98 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>234</v>
+        <v>1</v>
       </c>
       <c r="O206" t="n">
-        <v>234</v>
+        <v>1</v>
+      </c>
+      <c r="P206" t="n">
+        <v>1</v>
       </c>
       <c r="R206" t="n">
-        <v>0.06704189230680362</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S206" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO206" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR206" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS206" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ206" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37626,7 +37634,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -37661,7 +37669,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
@@ -37670,31 +37678,106 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P207" t="n">
-        <v>0</v>
-      </c>
-      <c r="R207" t="n">
-        <v>0</v>
-      </c>
-      <c r="S207" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U207" t="inlineStr">
         <is>
           <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
         </is>
       </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA207" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD207" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF207" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG207" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ207" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK207" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM207" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN207" t="b">
+        <v>1</v>
       </c>
       <c r="AO207" t="inlineStr">
         <is>
@@ -37788,17 +37871,17 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -37823,7 +37906,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
@@ -37832,173 +37915,81 @@
         </is>
       </c>
       <c r="N208" t="n">
+        <v>234</v>
+      </c>
+      <c r="O208" t="n">
+        <v>234</v>
+      </c>
+      <c r="R208" t="n">
+        <v>0.06704189230680362</v>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO208" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP208" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR208" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr"/>
+      <c r="AT208" t="n">
         <v>0</v>
       </c>
-      <c r="O208" t="n">
-        <v>0</v>
-      </c>
-      <c r="P208" t="n">
-        <v>0</v>
-      </c>
-      <c r="U208" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V208" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W208" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X208" t="inlineStr">
-        <is>
-          <t>Bacterial dysentery</t>
-        </is>
-      </c>
-      <c r="Y208" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z208" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA208" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB208" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC208" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD208" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE208" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF208" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG208" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH208" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI208" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ208" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK208" t="inlineStr">
-        <is>
-          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
-        </is>
-      </c>
-      <c r="AM208" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN208" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO208" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP208" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ208" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS208" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT208" t="n">
-        <v>1</v>
-      </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -38030,12 +38021,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -38060,90 +38051,107 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N209" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="O209" t="n">
-        <v>204</v>
+        <v>0</v>
+      </c>
+      <c r="P209" t="n">
+        <v>0</v>
       </c>
       <c r="R209" t="n">
-        <v>0.7492536111820371</v>
+        <v>0</v>
       </c>
       <c r="S209" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO209" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR209" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS209" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ209" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38170,17 +38178,17 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -38205,87 +38213,182 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N210" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O210" t="n">
-        <v>5</v>
-      </c>
-      <c r="S210" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P210" t="n">
+        <v>0</v>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X210" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD210" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE210" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF210" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG210" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH210" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI210" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ210" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK210" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM210" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN210" t="b">
+        <v>1</v>
       </c>
       <c r="AO210" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR210" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS210" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ210" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA210" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38317,12 +38420,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -38356,14 +38459,17 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>61</v>
+        <v>204</v>
       </c>
       <c r="O211" t="n">
-        <v>61</v>
+        <v>204</v>
+      </c>
+      <c r="R211" t="n">
+        <v>0.7492536111820371</v>
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO211" t="inlineStr">
@@ -38397,12 +38503,12 @@
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
@@ -38417,12 +38523,12 @@
       </c>
       <c r="BA211" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
@@ -38459,12 +38565,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -38498,10 +38604,10 @@
         </is>
       </c>
       <c r="N212" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="O212" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="S212" t="inlineStr">
         <is>
@@ -38539,7 +38645,7 @@
       </c>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
@@ -38559,7 +38665,7 @@
       </c>
       <c r="BA212" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB212" t="inlineStr">
@@ -38601,12 +38707,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -38640,10 +38746,10 @@
         </is>
       </c>
       <c r="N213" t="n">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="O213" t="n">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="S213" t="inlineStr">
         <is>
@@ -38681,7 +38787,7 @@
       </c>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
@@ -38701,7 +38807,7 @@
       </c>
       <c r="BA213" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB213" t="inlineStr">
@@ -38743,12 +38849,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -38782,10 +38888,10 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="O214" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="S214" t="inlineStr">
         <is>
@@ -38823,7 +38929,7 @@
       </c>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
@@ -38843,7 +38949,7 @@
       </c>
       <c r="BA214" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB214" t="inlineStr">
@@ -38885,12 +38991,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -38924,10 +39030,10 @@
         </is>
       </c>
       <c r="N215" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="O215" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="S215" t="inlineStr">
         <is>
@@ -38965,7 +39071,7 @@
       </c>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
@@ -38985,7 +39091,7 @@
       </c>
       <c r="BA215" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB215" t="inlineStr">
@@ -39027,12 +39133,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -39066,100 +39172,78 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="O216" t="n">
-        <v>1</v>
-      </c>
-      <c r="R216" t="n">
-        <v>0.01778809170864137</v>
+        <v>27</v>
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U216" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1210</t>
-        </is>
-      </c>
-      <c r="AA216" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO216" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP216" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ216" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR216" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS216" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1210</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS216" t="inlineStr"/>
       <c r="AT216" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU216" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV216" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA216" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB216" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC216" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -39186,17 +39270,17 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -39230,175 +39314,78 @@
         </is>
       </c>
       <c r="N217" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="O217" t="n">
-        <v>1</v>
-      </c>
-      <c r="U217" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1210</t>
-        </is>
-      </c>
-      <c r="V217" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1210</t>
-        </is>
-      </c>
-      <c r="W217" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X217" t="inlineStr">
-        <is>
-          <t>Shigella</t>
-        </is>
-      </c>
-      <c r="Y217" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z217" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA217" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB217" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC217" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD217" t="inlineStr">
+        <v>18</v>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO217" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP217" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR217" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS217" t="inlineStr"/>
+      <c r="AT217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU217" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV217" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE217" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF217" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG217" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH217" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI217" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ217" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK217" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1210.</t>
-        </is>
-      </c>
-      <c r="AM217" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN217" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO217" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP217" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ217" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR217" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS217" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1210</t>
-        </is>
-      </c>
-      <c r="AT217" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU217" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV217" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA217" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB217" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC217" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -39430,12 +39417,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -39469,13 +39456,13 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="O218" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R218" t="n">
-        <v>0.007751879695168184</v>
+        <v>0.2997402916894895</v>
       </c>
       <c r="S218" t="inlineStr">
         <is>
@@ -39508,42 +39495,42 @@
       </c>
       <c r="AV218" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA218" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB218" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC218" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -39575,12 +39562,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -39614,13 +39601,13 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="O219" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="R219" t="n">
-        <v>0.1945873408375057</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S219" t="inlineStr">
         <is>
@@ -39629,7 +39616,7 @@
       </c>
       <c r="U219" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1210</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -39649,7 +39636,7 @@
       </c>
       <c r="AQ219" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR219" t="inlineStr">
@@ -39659,7 +39646,7 @@
       </c>
       <c r="AS219" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1210</t>
         </is>
       </c>
       <c r="AT219" t="n">
@@ -39667,47 +39654,47 @@
       </c>
       <c r="AU219" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV219" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA219" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB219" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC219" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -39739,12 +39726,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -39778,29 +39765,29 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="O220" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="U220" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1210</t>
         </is>
       </c>
       <c r="V220" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1210</t>
         </is>
       </c>
       <c r="W220" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X220" t="inlineStr">
         <is>
-          <t>Shigellose</t>
+          <t>Shigella</t>
         </is>
       </c>
       <c r="Y220" t="inlineStr">
@@ -39825,7 +39812,7 @@
       </c>
       <c r="AC220" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD220" t="inlineStr">
@@ -39860,17 +39847,17 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 1210.</t>
         </is>
       </c>
       <c r="AM220" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN220" t="b">
@@ -39888,7 +39875,7 @@
       </c>
       <c r="AQ220" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR220" t="inlineStr">
@@ -39898,7 +39885,7 @@
       </c>
       <c r="AS220" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1210</t>
         </is>
       </c>
       <c r="AT220" t="n">
@@ -39906,47 +39893,47 @@
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV220" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA220" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB220" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC220" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -39978,12 +39965,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -40017,100 +40004,81 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>108</v>
+        <v>4</v>
       </c>
       <c r="O221" t="n">
-        <v>108</v>
+        <v>4</v>
       </c>
       <c r="R221" t="n">
-        <v>1.009247086254601</v>
+        <v>0.007751879695168184</v>
       </c>
       <c r="S221" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U221" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
-        </is>
-      </c>
-      <c r="AA221" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO221" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP221" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ221" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR221" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS221" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS221" t="inlineStr"/>
       <c r="AT221" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV221" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA221" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB221" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC221" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -40137,17 +40105,17 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -40181,39 +40149,22 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>108</v>
+        <v>11</v>
       </c>
       <c r="O222" t="n">
-        <v>108</v>
+        <v>11</v>
+      </c>
+      <c r="R222" t="n">
+        <v>0.1945873408375057</v>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U222" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
-        </is>
-      </c>
-      <c r="V222" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
-        </is>
-      </c>
-      <c r="W222" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X222" t="inlineStr">
-        <is>
-          <t>Shigellainfektion</t>
-        </is>
-      </c>
-      <c r="Y222" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z222" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -40221,64 +40172,6 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB222" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC222" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD222" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE222" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF222" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG222" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH222" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI222" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ222" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK222" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM222" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN222" t="b">
-        <v>1</v>
-      </c>
       <c r="AO222" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -40301,7 +40194,7 @@
       </c>
       <c r="AS222" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
+          <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
       <c r="AT222" t="n">
@@ -40314,42 +40207,42 @@
       </c>
       <c r="AV222" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA222" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -40376,17 +40269,17 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -40420,22 +40313,39 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="O223" t="n">
-        <v>4</v>
-      </c>
-      <c r="R223" t="n">
-        <v>0.01738276978574758</v>
-      </c>
-      <c r="S223" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>11</v>
       </c>
       <c r="U223" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_NO_FHI_502_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_502_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X223" t="inlineStr">
+        <is>
+          <t>Shigellose</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z223" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -40443,72 +40353,135 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB223" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD223" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE223" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF223" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG223" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH223" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI223" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ223" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK223" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM223" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN223" t="b">
+        <v>1</v>
+      </c>
       <c r="AO223" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ223" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR223" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS223" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
       <c r="AT223" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA223" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -40535,17 +40508,17 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -40579,39 +40552,22 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>4</v>
+        <v>108</v>
       </c>
       <c r="O224" t="n">
-        <v>4</v>
+        <v>108</v>
+      </c>
+      <c r="R224" t="n">
+        <v>1.009247086254601</v>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U224" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
-        </is>
-      </c>
-      <c r="V224" t="inlineStr">
-        <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
-        </is>
-      </c>
-      <c r="W224" t="inlineStr">
-        <is>
-          <t>SRC_TW_NIDSS</t>
-        </is>
-      </c>
-      <c r="X224" t="inlineStr">
-        <is>
-          <t>桿菌性痢疾</t>
-        </is>
-      </c>
-      <c r="Y224" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z224" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -40619,130 +40575,77 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB224" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC224" t="inlineStr">
-        <is>
-          <t>country:TW:national</t>
-        </is>
-      </c>
-      <c r="AD224" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE224" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF224" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG224" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH224" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI224" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ224" t="inlineStr">
-        <is>
-          <t>TW_NIDSS_004_current</t>
-        </is>
-      </c>
-      <c r="AK224" t="inlineStr">
-        <is>
-          <t>Taiwan NIDSS disease code 004, bacillary dysentery caused by Shigella; distinct from amoebiasis.</t>
-        </is>
-      </c>
-      <c r="AM224" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN224" t="b">
-        <v>1</v>
-      </c>
       <c r="AO224" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ224" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR224" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS224" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
       <c r="AT224" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -40769,17 +40672,17 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -40813,81 +40716,175 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>226</v>
+        <v>108</v>
       </c>
       <c r="O225" t="n">
-        <v>226</v>
-      </c>
-      <c r="R225" t="n">
-        <v>0.0647498618005881</v>
-      </c>
-      <c r="S225" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>108</v>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
+        </is>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X225" t="inlineStr">
+        <is>
+          <t>Shigellainfektion</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z225" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB225" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC225" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD225" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE225" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF225" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG225" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH225" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI225" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ225" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK225" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM225" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN225" t="b">
+        <v>1</v>
       </c>
       <c r="AO225" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ225" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR225" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS225" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS225" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
+        </is>
+      </c>
       <c r="AT225" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB225" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC225" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -40919,12 +40916,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -40949,7 +40946,7 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
@@ -40958,16 +40955,13 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O226" t="n">
-        <v>1</v>
-      </c>
-      <c r="P226" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R226" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.01738276978574758</v>
       </c>
       <c r="S226" t="inlineStr">
         <is>
@@ -40976,17 +40970,17 @@
       </c>
       <c r="U226" t="inlineStr">
         <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+          <t>SER_TW_SHIGELLOSIS_004</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO226" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP226" t="inlineStr">
@@ -40996,12 +40990,12 @@
       </c>
       <c r="AQ226" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS226" t="inlineStr">
         <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+          <t>SER_TW_SHIGELLOSIS_004</t>
         </is>
       </c>
       <c r="AT226" t="n">
@@ -41009,47 +41003,47 @@
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -41081,12 +41075,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -41111,7 +41105,7 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
@@ -41120,32 +41114,29 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O227" t="n">
-        <v>1</v>
-      </c>
-      <c r="P227" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U227" t="inlineStr">
         <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+          <t>SER_TW_SHIGELLOSIS_004</t>
         </is>
       </c>
       <c r="V227" t="inlineStr">
         <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+          <t>SER_TW_SHIGELLOSIS_004</t>
         </is>
       </c>
       <c r="W227" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_TW_NIDSS</t>
         </is>
       </c>
       <c r="X227" t="inlineStr">
         <is>
-          <t>Bacterial dysentery</t>
+          <t>桿菌性痢疾</t>
         </is>
       </c>
       <c r="Y227" t="inlineStr">
@@ -41160,7 +41151,7 @@
       </c>
       <c r="AA227" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB227" t="inlineStr">
@@ -41170,7 +41161,7 @@
       </c>
       <c r="AC227" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:TW:national</t>
         </is>
       </c>
       <c r="AD227" t="inlineStr">
@@ -41185,7 +41176,7 @@
       </c>
       <c r="AF227" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG227" t="inlineStr">
@@ -41205,12 +41196,12 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>TW_NIDSS_004_current</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
         <is>
-          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+          <t>Taiwan NIDSS disease code 004, bacillary dysentery caused by Shigella; distinct from amoebiasis.</t>
         </is>
       </c>
       <c r="AM227" t="inlineStr">
@@ -41223,7 +41214,7 @@
       </c>
       <c r="AO227" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP227" t="inlineStr">
@@ -41233,12 +41224,12 @@
       </c>
       <c r="AQ227" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS227" t="inlineStr">
         <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+          <t>SER_TW_SHIGELLOSIS_004</t>
         </is>
       </c>
       <c r="AT227" t="n">
@@ -41246,47 +41237,47 @@
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -41348,7 +41339,7 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
@@ -41357,13 +41348,13 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="O228" t="n">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="R228" t="n">
-        <v>0.06646888468024974</v>
+        <v>0.0647498618005881</v>
       </c>
       <c r="S228" t="inlineStr">
         <is>
@@ -41493,7 +41484,7 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
@@ -41655,7 +41646,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
@@ -41892,7 +41883,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
@@ -41901,13 +41892,13 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="O231" t="n">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="R231" t="n">
-        <v>0.06446335798731118</v>
+        <v>0.06646888468024974</v>
       </c>
       <c r="S231" t="inlineStr">
         <is>
@@ -42037,7 +42028,7 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
@@ -42046,16 +42037,16 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O232" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P232" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R232" t="n">
-        <v>0.003267233630263065</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S232" t="inlineStr">
         <is>
@@ -42199,7 +42190,7 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
@@ -42208,13 +42199,13 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O233" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P233" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U233" t="inlineStr">
         <is>
@@ -42436,7 +42427,7 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
@@ -42445,13 +42436,13 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="O234" t="n">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="R234" t="n">
-        <v>0.06131181604126484</v>
+        <v>0.06446335798731118</v>
       </c>
       <c r="S234" t="inlineStr">
         <is>
@@ -42581,7 +42572,7 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
@@ -42590,16 +42581,16 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O235" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P235" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R235" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.003267233630263065</v>
       </c>
       <c r="S235" t="inlineStr">
         <is>
@@ -42743,7 +42734,7 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
@@ -42752,13 +42743,13 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O236" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P236" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U236" t="inlineStr">
         <is>
@@ -42980,7 +42971,7 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
@@ -42989,13 +42980,13 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="O237" t="n">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="R237" t="n">
-        <v>0.05959279316160321</v>
+        <v>0.06131181604126484</v>
       </c>
       <c r="S237" t="inlineStr">
         <is>
@@ -43125,7 +43116,7 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
@@ -43134,16 +43125,16 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O238" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P238" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R238" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S238" t="inlineStr">
         <is>
@@ -43287,7 +43278,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -43296,13 +43287,13 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O239" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P239" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U239" t="inlineStr">
         <is>
@@ -43494,12 +43485,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -43524,22 +43515,22 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N240" t="n">
-        <v>7</v>
+        <v>208</v>
       </c>
       <c r="O240" t="n">
-        <v>7</v>
+        <v>208</v>
       </c>
       <c r="R240" t="n">
-        <v>0.02570968273663853</v>
+        <v>0.05959279316160321</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>
@@ -43572,42 +43563,42 @@
       </c>
       <c r="AV240" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA240" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB240" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC240" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -43639,12 +43630,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -43669,22 +43660,25 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N241" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O241" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="P241" t="n">
+        <v>2</v>
       </c>
       <c r="R241" t="n">
-        <v>0</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S241" t="inlineStr">
         <is>
@@ -43693,12 +43687,12 @@
       </c>
       <c r="U241" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1210</t>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO241" t="inlineStr">
@@ -43708,70 +43702,65 @@
       </c>
       <c r="AP241" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ241" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR241" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS241" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1210</t>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT241" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV241" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA241" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB241" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC241" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -43803,12 +43792,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -43833,38 +43822,41 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N242" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O242" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="P242" t="n">
+        <v>2</v>
       </c>
       <c r="U242" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1210</t>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
         </is>
       </c>
       <c r="V242" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1210</t>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
         </is>
       </c>
       <c r="W242" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X242" t="inlineStr">
         <is>
-          <t>Shigella</t>
+          <t>Bacterial dysentery</t>
         </is>
       </c>
       <c r="Y242" t="inlineStr">
@@ -43874,12 +43866,12 @@
       </c>
       <c r="Z242" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB242" t="inlineStr">
@@ -43889,7 +43881,7 @@
       </c>
       <c r="AC242" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD242" t="inlineStr">
@@ -43904,7 +43896,7 @@
       </c>
       <c r="AF242" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG242" t="inlineStr">
@@ -43924,12 +43916,12 @@
       </c>
       <c r="AJ242" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK242" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1210.</t>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
         </is>
       </c>
       <c r="AM242" t="inlineStr">
@@ -43947,70 +43939,65 @@
       </c>
       <c r="AP242" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ242" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR242" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS242" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1210</t>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT242" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU242" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV242" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA242" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB242" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC242" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -44042,12 +44029,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -44081,13 +44068,13 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O243" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R243" t="n">
-        <v>0</v>
+        <v>0.02570968273663853</v>
       </c>
       <c r="S243" t="inlineStr">
         <is>
@@ -44120,42 +44107,42 @@
       </c>
       <c r="AV243" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA243" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB243" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC243" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -44187,12 +44174,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -44226,13 +44213,13 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O244" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R244" t="n">
-        <v>0.01768975825795506</v>
+        <v>0</v>
       </c>
       <c r="S244" t="inlineStr">
         <is>
@@ -44241,7 +44228,7 @@
       </c>
       <c r="U244" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1210</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -44261,7 +44248,7 @@
       </c>
       <c r="AQ244" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR244" t="inlineStr">
@@ -44271,7 +44258,7 @@
       </c>
       <c r="AS244" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1210</t>
         </is>
       </c>
       <c r="AT244" t="n">
@@ -44279,47 +44266,47 @@
       </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV244" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA244" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB244" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC244" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -44351,12 +44338,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -44390,29 +44377,29 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U245" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1210</t>
         </is>
       </c>
       <c r="V245" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1210</t>
         </is>
       </c>
       <c r="W245" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X245" t="inlineStr">
         <is>
-          <t>Shigellose</t>
+          <t>Shigella</t>
         </is>
       </c>
       <c r="Y245" t="inlineStr">
@@ -44437,7 +44424,7 @@
       </c>
       <c r="AC245" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD245" t="inlineStr">
@@ -44472,17 +44459,17 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 1210.</t>
         </is>
       </c>
       <c r="AM245" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN245" t="b">
@@ -44500,7 +44487,7 @@
       </c>
       <c r="AQ245" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR245" t="inlineStr">
@@ -44510,7 +44497,7 @@
       </c>
       <c r="AS245" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1210</t>
         </is>
       </c>
       <c r="AT245" t="n">
@@ -44518,47 +44505,47 @@
       </c>
       <c r="AU245" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV245" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA245" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB245" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC245" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -44590,12 +44577,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -44620,7 +44607,7 @@
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
@@ -44629,13 +44616,13 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>198</v>
+        <v>0</v>
       </c>
       <c r="O246" t="n">
-        <v>198</v>
+        <v>0</v>
       </c>
       <c r="R246" t="n">
-        <v>0.05672775502883383</v>
+        <v>0</v>
       </c>
       <c r="S246" t="inlineStr">
         <is>
@@ -44668,40 +44655,588 @@
       </c>
       <c r="AV246" t="inlineStr">
         <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW246" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX246" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY246" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA246" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB246" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC246" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>shigellosis</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N247" t="n">
+        <v>1</v>
+      </c>
+      <c r="O247" t="n">
+        <v>1</v>
+      </c>
+      <c r="R247" t="n">
+        <v>0.01768975825795506</v>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_502_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO247" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP247" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ247" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR247" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS247" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_502_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT247" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU247" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV247" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW247" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX247" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY247" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA247" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB247" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC247" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>shigellosis</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N248" t="n">
+        <v>1</v>
+      </c>
+      <c r="O248" t="n">
+        <v>1</v>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_502_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_502_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W248" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X248" t="inlineStr">
+        <is>
+          <t>Shigellose</t>
+        </is>
+      </c>
+      <c r="Y248" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z248" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB248" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD248" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE248" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF248" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG248" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH248" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI248" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ248" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK248" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM248" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN248" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO248" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP248" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ248" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR248" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS248" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_502_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT248" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU248" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV248" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW248" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX248" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY248" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA248" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB248" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC248" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>shigellosis</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N249" t="n">
+        <v>198</v>
+      </c>
+      <c r="O249" t="n">
+        <v>198</v>
+      </c>
+      <c r="R249" t="n">
+        <v>0.05672775502883383</v>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO249" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP249" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR249" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS249" t="inlineStr"/>
+      <c r="AT249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU249" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV249" t="inlineStr">
+        <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW246" t="inlineStr">
+      <c r="AW249" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX246" t="inlineStr">
+      <c r="AX249" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY246" t="inlineStr">
+      <c r="AY249" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ246" t="inlineStr">
+      <c r="AZ249" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA246" t="inlineStr">
+      <c r="BA249" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB246" t="inlineStr">
+      <c r="BB249" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC246" t="inlineStr">
+      <c r="BC249" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -44823,7 +45358,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10">
@@ -44833,7 +45368,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -44853,7 +45388,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13">
@@ -44885,7 +45420,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9232</v>
+        <v>9286</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d105/2026-2029.xlsx
+++ b/diseases/d105/2026-2029.xlsx
@@ -38459,13 +38459,13 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="O211" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="R211" t="n">
-        <v>0.7492536111820371</v>
+        <v>0.7602720466405966</v>
       </c>
       <c r="S211" t="inlineStr">
         <is>
@@ -45420,7 +45420,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9286</v>
+        <v>9289</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d105/2026-2029.xlsx
+++ b/diseases/d105/2026-2029.xlsx
@@ -38459,13 +38459,13 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="O211" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="R211" t="n">
-        <v>0.7602720466405966</v>
+        <v>0.771290482099156</v>
       </c>
       <c r="S211" t="inlineStr">
         <is>
@@ -45420,7 +45420,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9289</v>
+        <v>9292</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d105/2026-2029.xlsx
+++ b/diseases/d105/2026-2029.xlsx
@@ -45242,6 +45242,405 @@
         </is>
       </c>
     </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>shigellosis</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N250" t="n">
+        <v>1</v>
+      </c>
+      <c r="O250" t="n">
+        <v>1</v>
+      </c>
+      <c r="P250" t="n">
+        <v>1</v>
+      </c>
+      <c r="R250" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO250" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP250" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ250" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS250" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT250" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU250" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV250" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW250" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX250" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY250" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA250" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB250" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC250" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>shigellosis</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N251" t="n">
+        <v>1</v>
+      </c>
+      <c r="O251" t="n">
+        <v>1</v>
+      </c>
+      <c r="P251" t="n">
+        <v>1</v>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W251" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X251" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y251" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z251" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB251" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC251" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD251" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE251" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF251" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG251" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH251" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI251" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ251" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK251" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM251" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN251" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO251" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP251" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ251" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS251" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT251" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU251" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV251" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW251" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX251" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY251" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA251" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB251" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC251" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -45275,7 +45674,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -45358,7 +45757,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10">
@@ -45368,7 +45767,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -45388,7 +45787,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13">
@@ -45420,7 +45819,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9292</v>
+        <v>9293</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d105/2026-2029.xlsx
+++ b/diseases/d105/2026-2029.xlsx
@@ -35094,13 +35094,13 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O193" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="R193" t="n">
-        <v>0.1891260466471829</v>
+        <v>0.1513008373177463</v>
       </c>
       <c r="S193" t="inlineStr">
         <is>
@@ -35253,10 +35253,10 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O194" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U194" t="inlineStr">
         <is>
@@ -40513,12 +40513,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -40552,13 +40552,13 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>108</v>
+        <v>4</v>
       </c>
       <c r="O224" t="n">
-        <v>108</v>
+        <v>4</v>
       </c>
       <c r="R224" t="n">
-        <v>1.009247086254601</v>
+        <v>0.07565041865887316</v>
       </c>
       <c r="S224" t="inlineStr">
         <is>
@@ -40567,7 +40567,7 @@
       </c>
       <c r="U224" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
+          <t>SER_NZ_SHIGELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -40582,7 +40582,7 @@
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ224" t="inlineStr">
@@ -40590,62 +40590,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR224" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS224" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
+          <t>SER_NZ_SHIGELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT224" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -40677,12 +40672,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -40716,29 +40711,29 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>108</v>
+        <v>4</v>
       </c>
       <c r="O225" t="n">
-        <v>108</v>
+        <v>4</v>
       </c>
       <c r="U225" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
+          <t>SER_NZ_SHIGELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V225" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
+          <t>SER_NZ_SHIGELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W225" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X225" t="inlineStr">
         <is>
-          <t>Shigellainfektion</t>
+          <t>Shigellosis</t>
         </is>
       </c>
       <c r="Y225" t="inlineStr">
@@ -40748,7 +40743,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -40763,7 +40758,7 @@
       </c>
       <c r="AC225" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD225" t="inlineStr">
@@ -40798,17 +40793,17 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>New Zealand PHF Science monthly shigellosis notifications.</t>
         </is>
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN225" t="b">
@@ -40821,7 +40816,7 @@
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ225" t="inlineStr">
@@ -40829,62 +40824,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR225" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS225" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
+          <t>SER_NZ_SHIGELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT225" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB225" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC225" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -40916,12 +40906,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -40955,13 +40945,13 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>4</v>
+        <v>108</v>
       </c>
       <c r="O226" t="n">
-        <v>4</v>
+        <v>108</v>
       </c>
       <c r="R226" t="n">
-        <v>0.01738276978574758</v>
+        <v>1.009247086254601</v>
       </c>
       <c r="S226" t="inlineStr">
         <is>
@@ -40970,7 +40960,7 @@
       </c>
       <c r="U226" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -40980,70 +40970,75 @@
       </c>
       <c r="AO226" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ226" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR226" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS226" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
       <c r="AT226" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -41075,12 +41070,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -41114,29 +41109,29 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>4</v>
+        <v>108</v>
       </c>
       <c r="O227" t="n">
-        <v>4</v>
+        <v>108</v>
       </c>
       <c r="U227" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
       <c r="V227" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
       <c r="W227" t="inlineStr">
         <is>
-          <t>SRC_TW_NIDSS</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X227" t="inlineStr">
         <is>
-          <t>桿菌性痢疾</t>
+          <t>Shigellainfektion</t>
         </is>
       </c>
       <c r="Y227" t="inlineStr">
@@ -41146,7 +41141,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -41161,7 +41156,7 @@
       </c>
       <c r="AC227" t="inlineStr">
         <is>
-          <t>country:TW:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD227" t="inlineStr">
@@ -41196,17 +41191,17 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>TW_NIDSS_004_current</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
         <is>
-          <t>Taiwan NIDSS disease code 004, bacillary dysentery caused by Shigella; distinct from amoebiasis.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
         </is>
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -41214,70 +41209,75 @@
       </c>
       <c r="AO227" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ227" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR227" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS227" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
       <c r="AT227" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -41309,12 +41309,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -41348,81 +41348,95 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>226</v>
+        <v>4</v>
       </c>
       <c r="O228" t="n">
-        <v>226</v>
+        <v>4</v>
       </c>
       <c r="R228" t="n">
-        <v>0.0647498618005881</v>
+        <v>0.01738276978574758</v>
       </c>
       <c r="S228" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>SER_TW_SHIGELLOSIS_004</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO228" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR228" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS228" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ228" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS228" t="inlineStr">
+        <is>
+          <t>SER_TW_SHIGELLOSIS_004</t>
+        </is>
+      </c>
       <c r="AT228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB228" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC228" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -41449,17 +41463,17 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -41484,7 +41498,7 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
@@ -41493,35 +41507,107 @@
         </is>
       </c>
       <c r="N229" t="n">
+        <v>4</v>
+      </c>
+      <c r="O229" t="n">
+        <v>4</v>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>SER_TW_SHIGELLOSIS_004</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>SER_TW_SHIGELLOSIS_004</t>
+        </is>
+      </c>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X229" t="inlineStr">
+        <is>
+          <t>桿菌性痢疾</t>
+        </is>
+      </c>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z229" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB229" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC229" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD229" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE229" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF229" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG229" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH229" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI229" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ229" t="inlineStr">
+        <is>
+          <t>TW_NIDSS_004_current</t>
+        </is>
+      </c>
+      <c r="AK229" t="inlineStr">
+        <is>
+          <t>Taiwan NIDSS disease code 004, bacillary dysentery caused by Shigella; distinct from amoebiasis.</t>
+        </is>
+      </c>
+      <c r="AM229" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN229" t="b">
         <v>1</v>
       </c>
-      <c r="O229" t="n">
-        <v>1</v>
-      </c>
-      <c r="P229" t="n">
-        <v>1</v>
-      </c>
-      <c r="R229" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S229" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U229" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA229" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO229" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP229" t="inlineStr">
@@ -41531,12 +41617,12 @@
       </c>
       <c r="AQ229" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS229" t="inlineStr">
         <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+          <t>SER_TW_SHIGELLOSIS_004</t>
         </is>
       </c>
       <c r="AT229" t="n">
@@ -41544,47 +41630,47 @@
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV229" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA229" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB229" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC229" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -41611,17 +41697,17 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -41646,7 +41732,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
@@ -41655,173 +41741,81 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>1</v>
+        <v>226</v>
       </c>
       <c r="O230" t="n">
-        <v>1</v>
-      </c>
-      <c r="P230" t="n">
-        <v>1</v>
-      </c>
-      <c r="U230" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V230" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W230" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X230" t="inlineStr">
-        <is>
-          <t>Bacterial dysentery</t>
-        </is>
-      </c>
-      <c r="Y230" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z230" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA230" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB230" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC230" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD230" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE230" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF230" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG230" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH230" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI230" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ230" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK230" t="inlineStr">
-        <is>
-          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
-        </is>
-      </c>
-      <c r="AM230" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN230" t="b">
-        <v>1</v>
+        <v>226</v>
+      </c>
+      <c r="R230" t="n">
+        <v>0.0647498618005881</v>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO230" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ230" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS230" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR230" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS230" t="inlineStr"/>
       <c r="AT230" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV230" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -41853,12 +41847,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -41883,7 +41877,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
@@ -41892,81 +41886,98 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>232</v>
+        <v>1</v>
       </c>
       <c r="O231" t="n">
-        <v>232</v>
+        <v>1</v>
+      </c>
+      <c r="P231" t="n">
+        <v>1</v>
       </c>
       <c r="R231" t="n">
-        <v>0.06646888468024974</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S231" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO231" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR231" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS231" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ231" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS231" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -41993,7 +42004,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -42028,7 +42039,7 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
@@ -42045,23 +42056,98 @@
       <c r="P232" t="n">
         <v>1</v>
       </c>
-      <c r="R232" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S232" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U232" t="inlineStr">
         <is>
           <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
         </is>
       </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X232" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y232" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z232" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA232" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB232" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD232" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE232" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF232" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG232" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH232" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI232" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ232" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK232" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM232" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN232" t="b">
+        <v>1</v>
       </c>
       <c r="AO232" t="inlineStr">
         <is>
@@ -42155,17 +42241,17 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -42190,7 +42276,7 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
@@ -42199,173 +42285,81 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>1</v>
+        <v>232</v>
       </c>
       <c r="O233" t="n">
-        <v>1</v>
-      </c>
-      <c r="P233" t="n">
-        <v>1</v>
-      </c>
-      <c r="U233" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V233" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W233" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X233" t="inlineStr">
-        <is>
-          <t>Bacterial dysentery</t>
-        </is>
-      </c>
-      <c r="Y233" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z233" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA233" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB233" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC233" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD233" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE233" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF233" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG233" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH233" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI233" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ233" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK233" t="inlineStr">
-        <is>
-          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
-        </is>
-      </c>
-      <c r="AM233" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN233" t="b">
-        <v>1</v>
+        <v>232</v>
+      </c>
+      <c r="R233" t="n">
+        <v>0.06646888468024974</v>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO233" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ233" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS233" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR233" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS233" t="inlineStr"/>
       <c r="AT233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA233" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB233" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC233" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -42397,12 +42391,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -42427,7 +42421,7 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
@@ -42436,81 +42430,98 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>225</v>
+        <v>1</v>
       </c>
       <c r="O234" t="n">
-        <v>225</v>
+        <v>1</v>
+      </c>
+      <c r="P234" t="n">
+        <v>1</v>
       </c>
       <c r="R234" t="n">
-        <v>0.06446335798731118</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S234" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO234" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR234" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS234" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ234" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS234" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT234" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA234" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB234" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC234" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -42537,7 +42548,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -42572,7 +42583,7 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
@@ -42581,31 +42592,106 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O235" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P235" t="n">
-        <v>4</v>
-      </c>
-      <c r="R235" t="n">
-        <v>0.003267233630263065</v>
-      </c>
-      <c r="S235" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U235" t="inlineStr">
         <is>
           <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
         </is>
       </c>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W235" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X235" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y235" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z235" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA235" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB235" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC235" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD235" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE235" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF235" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG235" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH235" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI235" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ235" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK235" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM235" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN235" t="b">
+        <v>1</v>
       </c>
       <c r="AO235" t="inlineStr">
         <is>
@@ -42699,17 +42785,17 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -42734,7 +42820,7 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
@@ -42743,173 +42829,81 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>4</v>
+        <v>225</v>
       </c>
       <c r="O236" t="n">
-        <v>4</v>
-      </c>
-      <c r="P236" t="n">
-        <v>4</v>
-      </c>
-      <c r="U236" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V236" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W236" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X236" t="inlineStr">
-        <is>
-          <t>Bacterial dysentery</t>
-        </is>
-      </c>
-      <c r="Y236" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z236" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA236" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB236" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC236" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD236" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE236" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF236" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG236" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH236" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI236" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ236" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK236" t="inlineStr">
-        <is>
-          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
-        </is>
-      </c>
-      <c r="AM236" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN236" t="b">
-        <v>1</v>
+        <v>225</v>
+      </c>
+      <c r="R236" t="n">
+        <v>0.06446335798731118</v>
+      </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO236" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ236" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS236" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR236" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS236" t="inlineStr"/>
       <c r="AT236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV236" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -42941,12 +42935,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -42971,7 +42965,7 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
@@ -42980,81 +42974,98 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>214</v>
+        <v>4</v>
       </c>
       <c r="O237" t="n">
-        <v>214</v>
+        <v>4</v>
+      </c>
+      <c r="P237" t="n">
+        <v>4</v>
       </c>
       <c r="R237" t="n">
-        <v>0.06131181604126484</v>
+        <v>0.003267233630263065</v>
       </c>
       <c r="S237" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO237" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR237" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS237" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ237" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS237" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT237" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -43081,7 +43092,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -43116,7 +43127,7 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
@@ -43125,31 +43136,106 @@
         </is>
       </c>
       <c r="N238" t="n">
+        <v>4</v>
+      </c>
+      <c r="O238" t="n">
+        <v>4</v>
+      </c>
+      <c r="P238" t="n">
+        <v>4</v>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X238" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z238" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB238" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC238" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD238" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE238" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF238" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG238" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH238" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI238" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ238" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK238" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM238" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN238" t="b">
         <v>1</v>
-      </c>
-      <c r="O238" t="n">
-        <v>1</v>
-      </c>
-      <c r="P238" t="n">
-        <v>1</v>
-      </c>
-      <c r="R238" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S238" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U238" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA238" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
       </c>
       <c r="AO238" t="inlineStr">
         <is>
@@ -43243,17 +43329,17 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -43278,7 +43364,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -43287,173 +43373,81 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>1</v>
+        <v>214</v>
       </c>
       <c r="O239" t="n">
-        <v>1</v>
-      </c>
-      <c r="P239" t="n">
-        <v>1</v>
-      </c>
-      <c r="U239" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V239" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W239" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X239" t="inlineStr">
-        <is>
-          <t>Bacterial dysentery</t>
-        </is>
-      </c>
-      <c r="Y239" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z239" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA239" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB239" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC239" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD239" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE239" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF239" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG239" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH239" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI239" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ239" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK239" t="inlineStr">
-        <is>
-          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
-        </is>
-      </c>
-      <c r="AM239" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN239" t="b">
-        <v>1</v>
+        <v>214</v>
+      </c>
+      <c r="R239" t="n">
+        <v>0.06131181604126484</v>
+      </c>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO239" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP239" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ239" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS239" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR239" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS239" t="inlineStr"/>
       <c r="AT239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV239" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA239" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB239" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC239" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -43485,12 +43479,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -43515,7 +43509,7 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
@@ -43524,81 +43518,98 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>208</v>
+        <v>1</v>
       </c>
       <c r="O240" t="n">
-        <v>208</v>
+        <v>1</v>
+      </c>
+      <c r="P240" t="n">
+        <v>1</v>
       </c>
       <c r="R240" t="n">
-        <v>0.05959279316160321</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO240" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP240" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR240" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS240" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ240" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS240" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV240" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA240" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB240" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC240" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -43625,7 +43636,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -43660,7 +43671,7 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
@@ -43669,31 +43680,106 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O241" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P241" t="n">
-        <v>2</v>
-      </c>
-      <c r="R241" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="S241" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U241" t="inlineStr">
         <is>
           <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
         </is>
       </c>
+      <c r="V241" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W241" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X241" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y241" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z241" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA241" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB241" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC241" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD241" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE241" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF241" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG241" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH241" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI241" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ241" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK241" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM241" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN241" t="b">
+        <v>1</v>
       </c>
       <c r="AO241" t="inlineStr">
         <is>
@@ -43787,17 +43873,17 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -43822,7 +43908,7 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
@@ -43831,173 +43917,81 @@
         </is>
       </c>
       <c r="N242" t="n">
-        <v>2</v>
+        <v>208</v>
       </c>
       <c r="O242" t="n">
-        <v>2</v>
-      </c>
-      <c r="P242" t="n">
-        <v>2</v>
-      </c>
-      <c r="U242" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V242" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W242" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X242" t="inlineStr">
-        <is>
-          <t>Bacterial dysentery</t>
-        </is>
-      </c>
-      <c r="Y242" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z242" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA242" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB242" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC242" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD242" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE242" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF242" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG242" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH242" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI242" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ242" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK242" t="inlineStr">
-        <is>
-          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
-        </is>
-      </c>
-      <c r="AM242" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN242" t="b">
-        <v>1</v>
+        <v>208</v>
+      </c>
+      <c r="R242" t="n">
+        <v>0.05959279316160321</v>
+      </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO242" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP242" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ242" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS242" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR242" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS242" t="inlineStr"/>
       <c r="AT242" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU242" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV242" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA242" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB242" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC242" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -44029,12 +44023,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -44059,90 +44053,107 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N243" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O243" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="P243" t="n">
+        <v>2</v>
       </c>
       <c r="R243" t="n">
-        <v>0.02570968273663853</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S243" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO243" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP243" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR243" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS243" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ243" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS243" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT243" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU243" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV243" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA243" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB243" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC243" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -44169,17 +44180,17 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -44204,37 +44215,115 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N244" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O244" t="n">
-        <v>0</v>
-      </c>
-      <c r="R244" t="n">
-        <v>0</v>
-      </c>
-      <c r="S244" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P244" t="n">
+        <v>2</v>
       </c>
       <c r="U244" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1210</t>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W244" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X244" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y244" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z244" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB244" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC244" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD244" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE244" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF244" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG244" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH244" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI244" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ244" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK244" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM244" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN244" t="b">
+        <v>1</v>
       </c>
       <c r="AO244" t="inlineStr">
         <is>
@@ -44243,70 +44332,65 @@
       </c>
       <c r="AP244" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ244" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR244" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS244" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1210</t>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT244" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV244" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA244" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB244" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC244" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -44333,17 +44417,17 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -44377,175 +44461,81 @@
         </is>
       </c>
       <c r="N245" t="n">
+        <v>7</v>
+      </c>
+      <c r="O245" t="n">
+        <v>7</v>
+      </c>
+      <c r="R245" t="n">
+        <v>0.02570968273663853</v>
+      </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO245" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP245" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR245" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS245" t="inlineStr"/>
+      <c r="AT245" t="n">
         <v>0</v>
       </c>
-      <c r="O245" t="n">
-        <v>0</v>
-      </c>
-      <c r="U245" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1210</t>
-        </is>
-      </c>
-      <c r="V245" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1210</t>
-        </is>
-      </c>
-      <c r="W245" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X245" t="inlineStr">
-        <is>
-          <t>Shigella</t>
-        </is>
-      </c>
-      <c r="Y245" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z245" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA245" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB245" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC245" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD245" t="inlineStr">
+      <c r="AU245" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV245" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE245" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF245" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG245" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH245" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI245" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ245" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK245" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1210.</t>
-        </is>
-      </c>
-      <c r="AM245" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN245" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO245" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP245" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ245" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR245" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS245" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1210</t>
-        </is>
-      </c>
-      <c r="AT245" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU245" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV245" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA245" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB245" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC245" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -44577,12 +44567,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -44629,68 +44619,87 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1210</t>
+        </is>
+      </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO246" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP246" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ246" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR246" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS246" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS246" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1210</t>
+        </is>
+      </c>
       <c r="AT246" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU246" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV246" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA246" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB246" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC246" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -44717,17 +44726,17 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -44761,29 +44770,104 @@
         </is>
       </c>
       <c r="N247" t="n">
+        <v>0</v>
+      </c>
+      <c r="O247" t="n">
+        <v>0</v>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1210</t>
+        </is>
+      </c>
+      <c r="V247" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1210</t>
+        </is>
+      </c>
+      <c r="W247" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X247" t="inlineStr">
+        <is>
+          <t>Shigella</t>
+        </is>
+      </c>
+      <c r="Y247" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z247" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB247" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC247" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD247" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE247" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF247" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG247" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH247" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI247" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ247" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK247" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1210.</t>
+        </is>
+      </c>
+      <c r="AM247" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN247" t="b">
         <v>1</v>
       </c>
-      <c r="O247" t="n">
-        <v>1</v>
-      </c>
-      <c r="R247" t="n">
-        <v>0.01768975825795506</v>
-      </c>
-      <c r="S247" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U247" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA247" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO247" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -44796,7 +44880,7 @@
       </c>
       <c r="AQ247" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR247" t="inlineStr">
@@ -44806,7 +44890,7 @@
       </c>
       <c r="AS247" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1210</t>
         </is>
       </c>
       <c r="AT247" t="n">
@@ -44814,47 +44898,47 @@
       </c>
       <c r="AU247" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV247" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA247" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB247" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC247" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -44881,17 +44965,17 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -44925,175 +45009,81 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O248" t="n">
-        <v>1</v>
-      </c>
-      <c r="U248" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V248" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W248" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X248" t="inlineStr">
-        <is>
-          <t>Shigellose</t>
-        </is>
-      </c>
-      <c r="Y248" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z248" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA248" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB248" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC248" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD248" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE248" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF248" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG248" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH248" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI248" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ248" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK248" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM248" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN248" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R248" t="n">
+        <v>0</v>
+      </c>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO248" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ248" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR248" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS248" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS248" t="inlineStr"/>
       <c r="AT248" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -45125,12 +45115,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -45155,7 +45145,7 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
@@ -45164,81 +45154,100 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>198</v>
+        <v>1</v>
       </c>
       <c r="O249" t="n">
-        <v>198</v>
+        <v>1</v>
       </c>
       <c r="R249" t="n">
-        <v>0.05672775502883383</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S249" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_502_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO249" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ249" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR249" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS249" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS249" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_502_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT249" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV249" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA249" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB249" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC249" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -45265,17 +45274,17 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -45300,7 +45309,7 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
@@ -45314,27 +45323,99 @@
       <c r="O250" t="n">
         <v>1</v>
       </c>
-      <c r="P250" t="n">
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_502_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_502_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X250" t="inlineStr">
+        <is>
+          <t>Shigellose</t>
+        </is>
+      </c>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z250" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB250" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD250" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE250" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF250" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG250" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH250" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI250" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ250" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK250" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM250" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN250" t="b">
         <v>1</v>
       </c>
-      <c r="R250" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S250" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U250" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA250" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO250" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -45342,7 +45423,7 @@
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ250" t="inlineStr">
@@ -45350,57 +45431,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR250" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS250" t="inlineStr">
         <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+          <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
       <c r="AT250" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV250" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA250" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB250" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC250" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -45427,215 +45513,522 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N251" t="n">
+        <v>198</v>
+      </c>
+      <c r="O251" t="n">
+        <v>198</v>
+      </c>
+      <c r="R251" t="n">
+        <v>0.05672775502883383</v>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO251" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP251" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR251" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS251" t="inlineStr"/>
+      <c r="AT251" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU251" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV251" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW251" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX251" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY251" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA251" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB251" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC251" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>shigellosis</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N252" t="n">
+        <v>1</v>
+      </c>
+      <c r="O252" t="n">
+        <v>1</v>
+      </c>
+      <c r="P252" t="n">
+        <v>1</v>
+      </c>
+      <c r="R252" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO252" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP252" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ252" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS252" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT252" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU252" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV252" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW252" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX252" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY252" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA252" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB252" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC252" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>shigellosis</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F251" t="inlineStr">
+      <c r="F253" t="inlineStr">
         <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="G251" t="inlineStr">
+      <c r="G253" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>D105</t>
-        </is>
-      </c>
-      <c r="I251" t="inlineStr">
-        <is>
-          <t>Shigellosis</t>
-        </is>
-      </c>
-      <c r="J251" t="inlineStr">
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
         <is>
           <t>志贺菌病</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr">
+      <c r="K253" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L251" t="inlineStr">
+      <c r="L253" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="M251" t="inlineStr">
+      <c r="M253" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N251" t="n">
+      <c r="N253" t="n">
         <v>1</v>
       </c>
-      <c r="O251" t="n">
+      <c r="O253" t="n">
         <v>1</v>
       </c>
-      <c r="P251" t="n">
+      <c r="P253" t="n">
         <v>1</v>
       </c>
-      <c r="U251" t="inlineStr">
+      <c r="U253" t="inlineStr">
         <is>
           <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V251" t="inlineStr">
+      <c r="V253" t="inlineStr">
         <is>
           <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
         </is>
       </c>
-      <c r="W251" t="inlineStr">
+      <c r="W253" t="inlineStr">
         <is>
           <t>SRC_JP_NIID</t>
         </is>
       </c>
-      <c r="X251" t="inlineStr">
+      <c r="X253" t="inlineStr">
         <is>
           <t>Bacterial dysentery</t>
         </is>
       </c>
-      <c r="Y251" t="inlineStr">
+      <c r="Y253" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z251" t="inlineStr">
+      <c r="Z253" t="inlineStr">
         <is>
           <t>notification</t>
         </is>
       </c>
-      <c r="AA251" t="inlineStr">
+      <c r="AA253" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
       </c>
-      <c r="AB251" t="inlineStr">
+      <c r="AB253" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC251" t="inlineStr">
+      <c r="AC253" t="inlineStr">
         <is>
           <t>country:JP:national</t>
         </is>
       </c>
-      <c r="AD251" t="inlineStr">
+      <c r="AD253" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE251" t="inlineStr">
+      <c r="AE253" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF251" t="inlineStr">
+      <c r="AF253" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="AG251" t="inlineStr">
+      <c r="AG253" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH251" t="inlineStr">
+      <c r="AH253" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI251" t="inlineStr">
+      <c r="AI253" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ251" t="inlineStr">
+      <c r="AJ253" t="inlineStr">
         <is>
           <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
-      <c r="AK251" t="inlineStr">
+      <c r="AK253" t="inlineStr">
         <is>
           <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
         </is>
       </c>
-      <c r="AM251" t="inlineStr">
+      <c r="AM253" t="inlineStr">
         <is>
           <t>provisional; raw</t>
         </is>
       </c>
-      <c r="AN251" t="b">
+      <c r="AN253" t="b">
         <v>1</v>
       </c>
-      <c r="AO251" t="inlineStr">
+      <c r="AO253" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP251" t="inlineStr">
+      <c r="AP253" t="inlineStr">
         <is>
           <t>single_series</t>
         </is>
       </c>
-      <c r="AQ251" t="inlineStr">
+      <c r="AQ253" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AS251" t="inlineStr">
+      <c r="AS253" t="inlineStr">
         <is>
           <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
         </is>
       </c>
-      <c r="AT251" t="n">
+      <c r="AT253" t="n">
         <v>1</v>
       </c>
-      <c r="AU251" t="inlineStr">
+      <c r="AU253" t="inlineStr">
         <is>
           <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
-      <c r="AV251" t="inlineStr">
+      <c r="AV253" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW251" t="inlineStr">
+      <c r="AW253" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX251" t="inlineStr">
+      <c r="AX253" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY251" t="inlineStr">
+      <c r="AY253" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ251" t="inlineStr">
+      <c r="AZ253" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA251" t="inlineStr">
+      <c r="BA253" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB251" t="inlineStr">
+      <c r="BB253" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC251" t="inlineStr">
+      <c r="BC253" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -45757,7 +46150,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10">
@@ -45767,7 +46160,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -45787,7 +46180,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13">
@@ -45819,7 +46212,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9293</v>
+        <v>9295</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d105/2026-2029.xlsx
+++ b/diseases/d105/2026-2029.xlsx
@@ -45154,13 +45154,13 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O249" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R249" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.07075903303182025</v>
       </c>
       <c r="S249" t="inlineStr">
         <is>
@@ -45318,10 +45318,10 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O250" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U250" t="inlineStr">
         <is>
@@ -46212,7 +46212,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9295</v>
+        <v>9298</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d105/2026-2029.xlsx
+++ b/diseases/d105/2026-2029.xlsx
@@ -32324,13 +32324,13 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O176" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="R176" t="n">
-        <v>0.752926423001557</v>
+        <v>0.7565992348210768</v>
       </c>
       <c r="S176" t="inlineStr">
         <is>
@@ -38459,13 +38459,13 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="O211" t="n">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="R211" t="n">
-        <v>0.771290482099156</v>
+        <v>0.7859817293772351</v>
       </c>
       <c r="S211" t="inlineStr">
         <is>
@@ -46031,6 +46031,151 @@
       <c r="BC253" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>shigellosis</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N254" t="n">
+        <v>180</v>
+      </c>
+      <c r="O254" t="n">
+        <v>180</v>
+      </c>
+      <c r="R254" t="n">
+        <v>0.05157068638984894</v>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO254" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP254" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR254" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS254" t="inlineStr"/>
+      <c r="AT254" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU254" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV254" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW254" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX254" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY254" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA254" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB254" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC254" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -46067,7 +46212,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -46150,7 +46295,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10">
@@ -46160,7 +46305,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
@@ -46212,7 +46357,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9298</v>
+        <v>9483</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d105/2026-2029.xlsx
+++ b/diseases/d105/2026-2029.xlsx
@@ -38459,13 +38459,13 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O211" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="R211" t="n">
-        <v>0.7859817293772351</v>
+        <v>0.7896545411967548</v>
       </c>
       <c r="S211" t="inlineStr">
         <is>
@@ -46357,7 +46357,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9483</v>
+        <v>9484</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d105/2026-2029.xlsx
+++ b/diseases/d105/2026-2029.xlsx
@@ -3895,7 +3895,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -9370,7 +9370,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -9917,7 +9917,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -10464,7 +10464,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12242,7 +12242,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -14298,7 +14298,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -14845,7 +14845,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -15392,7 +15392,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -15939,7 +15939,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -19217,7 +19217,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -19764,7 +19764,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -20311,7 +20311,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -20858,7 +20858,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -24136,7 +24136,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -24683,7 +24683,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -25230,7 +25230,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -25777,7 +25777,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -26321,7 +26321,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -30540,7 +30540,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -31084,7 +31084,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -31628,7 +31628,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
@@ -32172,7 +32172,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -36675,7 +36675,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -37219,7 +37219,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK204" t="inlineStr">
@@ -37763,7 +37763,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -38307,7 +38307,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
@@ -38459,13 +38459,13 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="O211" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="R211" t="n">
-        <v>0.7896545411967548</v>
+        <v>0.7970001648357945</v>
       </c>
       <c r="S211" t="inlineStr">
         <is>
@@ -39965,12 +39965,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -40004,13 +40004,13 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O221" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R221" t="n">
-        <v>0.007751879695168184</v>
+        <v>0</v>
       </c>
       <c r="S221" t="inlineStr">
         <is>
@@ -40043,42 +40043,42 @@
       </c>
       <c r="AV221" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA221" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB221" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC221" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -40110,12 +40110,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -40149,100 +40149,81 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="O222" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="R222" t="n">
-        <v>0.1945873408375057</v>
+        <v>0.007751879695168184</v>
       </c>
       <c r="S222" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U222" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA222" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO222" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ222" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR222" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS222" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS222" t="inlineStr"/>
       <c r="AT222" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA222" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -40269,7 +40250,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -40318,98 +40299,23 @@
       <c r="O223" t="n">
         <v>11</v>
       </c>
+      <c r="R223" t="n">
+        <v>0.1945873408375057</v>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U223" t="inlineStr">
         <is>
           <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
-      <c r="V223" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W223" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X223" t="inlineStr">
-        <is>
-          <t>Shigellose</t>
-        </is>
-      </c>
-      <c r="Y223" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z223" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA223" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB223" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC223" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD223" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE223" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF223" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG223" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH223" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI223" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ223" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK223" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM223" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN223" t="b">
-        <v>1</v>
       </c>
       <c r="AO223" t="inlineStr">
         <is>
@@ -40508,17 +40414,17 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -40552,22 +40458,39 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="O224" t="n">
-        <v>4</v>
-      </c>
-      <c r="R224" t="n">
-        <v>0.07565041865887316</v>
-      </c>
-      <c r="S224" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>11</v>
       </c>
       <c r="U224" t="inlineStr">
         <is>
-          <t>SER_NZ_SHIGELLOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_502_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_502_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X224" t="inlineStr">
+        <is>
+          <t>Shigellose</t>
+        </is>
+      </c>
+      <c r="Y224" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z224" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -40575,6 +40498,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB224" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD224" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE224" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF224" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG224" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH224" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI224" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ224" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK224" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM224" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN224" t="b">
+        <v>1</v>
+      </c>
       <c r="AO224" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -40582,7 +40563,7 @@
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ224" t="inlineStr">
@@ -40590,57 +40571,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR224" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS224" t="inlineStr">
         <is>
-          <t>SER_NZ_SHIGELLOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
       <c r="AT224" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -40667,7 +40653,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -40716,98 +40702,23 @@
       <c r="O225" t="n">
         <v>4</v>
       </c>
+      <c r="R225" t="n">
+        <v>0.07565041865887316</v>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U225" t="inlineStr">
         <is>
           <t>SER_NZ_SHIGELLOSIS_MONTHLY</t>
         </is>
       </c>
-      <c r="V225" t="inlineStr">
-        <is>
-          <t>SER_NZ_SHIGELLOSIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W225" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X225" t="inlineStr">
-        <is>
-          <t>Shigellosis</t>
-        </is>
-      </c>
-      <c r="Y225" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z225" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA225" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB225" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC225" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD225" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE225" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF225" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG225" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH225" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI225" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ225" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK225" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly shigellosis notifications.</t>
-        </is>
-      </c>
-      <c r="AM225" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN225" t="b">
-        <v>1</v>
       </c>
       <c r="AO225" t="inlineStr">
         <is>
@@ -40901,17 +40812,17 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -40945,22 +40856,39 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>108</v>
+        <v>4</v>
       </c>
       <c r="O226" t="n">
-        <v>108</v>
-      </c>
-      <c r="R226" t="n">
-        <v>1.009247086254601</v>
-      </c>
-      <c r="S226" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
       </c>
       <c r="U226" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
+          <t>SER_NZ_SHIGELLOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>SER_NZ_SHIGELLOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X226" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -40968,6 +40896,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB226" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD226" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE226" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF226" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG226" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH226" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI226" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ226" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK226" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly shigellosis notifications.</t>
+        </is>
+      </c>
+      <c r="AM226" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN226" t="b">
+        <v>1</v>
+      </c>
       <c r="AO226" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -40975,7 +40961,7 @@
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ226" t="inlineStr">
@@ -40983,62 +40969,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR226" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS226" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
+          <t>SER_NZ_SHIGELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT226" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -41065,7 +41046,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -41114,98 +41095,23 @@
       <c r="O227" t="n">
         <v>108</v>
       </c>
+      <c r="R227" t="n">
+        <v>1.009247086254601</v>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U227" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
-      <c r="V227" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
-        </is>
-      </c>
-      <c r="W227" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X227" t="inlineStr">
-        <is>
-          <t>Shigellainfektion</t>
-        </is>
-      </c>
-      <c r="Y227" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z227" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA227" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB227" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC227" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD227" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE227" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF227" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG227" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH227" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI227" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ227" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK227" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM227" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN227" t="b">
-        <v>1</v>
       </c>
       <c r="AO227" t="inlineStr">
         <is>
@@ -41304,17 +41210,17 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -41348,22 +41254,39 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>4</v>
+        <v>108</v>
       </c>
       <c r="O228" t="n">
-        <v>4</v>
-      </c>
-      <c r="R228" t="n">
-        <v>0.01738276978574758</v>
-      </c>
-      <c r="S228" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>108</v>
       </c>
       <c r="U228" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
+        </is>
+      </c>
+      <c r="W228" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X228" t="inlineStr">
+        <is>
+          <t>Shigellainfektion</t>
+        </is>
+      </c>
+      <c r="Y228" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z228" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -41371,72 +41294,135 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB228" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC228" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD228" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE228" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF228" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG228" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH228" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI228" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ228" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK228" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM228" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN228" t="b">
+        <v>1</v>
+      </c>
       <c r="AO228" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ228" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR228" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS228" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
       <c r="AT228" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB228" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC228" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -41463,7 +41449,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -41512,98 +41498,23 @@
       <c r="O229" t="n">
         <v>4</v>
       </c>
+      <c r="R229" t="n">
+        <v>0.01738276978574758</v>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U229" t="inlineStr">
         <is>
           <t>SER_TW_SHIGELLOSIS_004</t>
         </is>
       </c>
-      <c r="V229" t="inlineStr">
-        <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
-        </is>
-      </c>
-      <c r="W229" t="inlineStr">
-        <is>
-          <t>SRC_TW_NIDSS</t>
-        </is>
-      </c>
-      <c r="X229" t="inlineStr">
-        <is>
-          <t>桿菌性痢疾</t>
-        </is>
-      </c>
-      <c r="Y229" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z229" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA229" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB229" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC229" t="inlineStr">
-        <is>
-          <t>country:TW:national</t>
-        </is>
-      </c>
-      <c r="AD229" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE229" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF229" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG229" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH229" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI229" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ229" t="inlineStr">
-        <is>
-          <t>TW_NIDSS_004_current</t>
-        </is>
-      </c>
-      <c r="AK229" t="inlineStr">
-        <is>
-          <t>Taiwan NIDSS disease code 004, bacillary dysentery caused by Shigella; distinct from amoebiasis.</t>
-        </is>
-      </c>
-      <c r="AM229" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN229" t="b">
-        <v>1</v>
       </c>
       <c r="AO229" t="inlineStr">
         <is>
@@ -41697,17 +41608,17 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -41741,81 +41652,170 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>226</v>
+        <v>4</v>
       </c>
       <c r="O230" t="n">
-        <v>226</v>
-      </c>
-      <c r="R230" t="n">
-        <v>0.0647498618005881</v>
-      </c>
-      <c r="S230" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>SER_TW_SHIGELLOSIS_004</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>SER_TW_SHIGELLOSIS_004</t>
+        </is>
+      </c>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X230" t="inlineStr">
+        <is>
+          <t>桿菌性痢疾</t>
+        </is>
+      </c>
+      <c r="Y230" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z230" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB230" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC230" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD230" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE230" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF230" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG230" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH230" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI230" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ230" t="inlineStr">
+        <is>
+          <t>TW_NIDSS_004_current</t>
+        </is>
+      </c>
+      <c r="AK230" t="inlineStr">
+        <is>
+          <t>Taiwan NIDSS disease code 004, bacillary dysentery caused by Shigella; distinct from amoebiasis.</t>
+        </is>
+      </c>
+      <c r="AM230" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN230" t="b">
+        <v>1</v>
       </c>
       <c r="AO230" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR230" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS230" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ230" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS230" t="inlineStr">
+        <is>
+          <t>SER_TW_SHIGELLOSIS_004</t>
+        </is>
+      </c>
       <c r="AT230" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV230" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -41847,12 +41847,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -41877,7 +41877,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
@@ -41886,98 +41886,81 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>1</v>
+        <v>226</v>
       </c>
       <c r="O231" t="n">
-        <v>1</v>
-      </c>
-      <c r="P231" t="n">
-        <v>1</v>
+        <v>226</v>
       </c>
       <c r="R231" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.0647498618005881</v>
       </c>
       <c r="S231" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U231" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA231" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO231" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ231" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS231" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR231" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS231" t="inlineStr"/>
       <c r="AT231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -42004,7 +41987,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -42056,98 +42039,23 @@
       <c r="P232" t="n">
         <v>1</v>
       </c>
+      <c r="R232" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U232" t="inlineStr">
         <is>
           <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V232" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W232" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X232" t="inlineStr">
-        <is>
-          <t>Bacterial dysentery</t>
-        </is>
-      </c>
-      <c r="Y232" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z232" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA232" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB232" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC232" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD232" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE232" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF232" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG232" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH232" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI232" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ232" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK232" t="inlineStr">
-        <is>
-          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
-        </is>
-      </c>
-      <c r="AM232" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN232" t="b">
-        <v>1</v>
       </c>
       <c r="AO232" t="inlineStr">
         <is>
@@ -42241,17 +42149,17 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -42276,7 +42184,7 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
@@ -42285,81 +42193,173 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>232</v>
+        <v>1</v>
       </c>
       <c r="O233" t="n">
-        <v>232</v>
-      </c>
-      <c r="R233" t="n">
-        <v>0.06646888468024974</v>
-      </c>
-      <c r="S233" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P233" t="n">
+        <v>1</v>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X233" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y233" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z233" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB233" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD233" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE233" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF233" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG233" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH233" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI233" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ233" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK233" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM233" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN233" t="b">
+        <v>1</v>
       </c>
       <c r="AO233" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR233" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS233" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ233" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS233" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA233" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB233" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC233" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -42391,12 +42391,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -42421,7 +42421,7 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
@@ -42430,98 +42430,81 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>1</v>
+        <v>232</v>
       </c>
       <c r="O234" t="n">
-        <v>1</v>
-      </c>
-      <c r="P234" t="n">
-        <v>1</v>
+        <v>232</v>
       </c>
       <c r="R234" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.06646888468024974</v>
       </c>
       <c r="S234" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U234" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA234" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO234" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ234" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS234" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR234" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS234" t="inlineStr"/>
       <c r="AT234" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA234" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB234" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC234" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -42548,7 +42531,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -42600,98 +42583,23 @@
       <c r="P235" t="n">
         <v>1</v>
       </c>
+      <c r="R235" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U235" t="inlineStr">
         <is>
           <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V235" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W235" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X235" t="inlineStr">
-        <is>
-          <t>Bacterial dysentery</t>
-        </is>
-      </c>
-      <c r="Y235" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z235" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA235" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB235" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC235" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD235" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE235" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF235" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG235" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH235" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI235" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ235" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK235" t="inlineStr">
-        <is>
-          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
-        </is>
-      </c>
-      <c r="AM235" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN235" t="b">
-        <v>1</v>
       </c>
       <c r="AO235" t="inlineStr">
         <is>
@@ -42785,17 +42693,17 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -42820,7 +42728,7 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
@@ -42829,81 +42737,173 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>225</v>
+        <v>1</v>
       </c>
       <c r="O236" t="n">
-        <v>225</v>
-      </c>
-      <c r="R236" t="n">
-        <v>0.06446335798731118</v>
-      </c>
-      <c r="S236" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P236" t="n">
+        <v>1</v>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W236" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X236" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y236" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z236" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB236" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC236" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD236" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE236" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF236" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG236" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH236" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI236" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ236" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK236" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM236" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN236" t="b">
+        <v>1</v>
       </c>
       <c r="AO236" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR236" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS236" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ236" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS236" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV236" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -42935,12 +42935,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -42965,7 +42965,7 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
@@ -42974,98 +42974,81 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>4</v>
+        <v>225</v>
       </c>
       <c r="O237" t="n">
-        <v>4</v>
-      </c>
-      <c r="P237" t="n">
-        <v>4</v>
+        <v>225</v>
       </c>
       <c r="R237" t="n">
-        <v>0.003267233630263065</v>
+        <v>0.06446335798731118</v>
       </c>
       <c r="S237" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U237" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA237" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO237" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ237" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS237" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR237" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS237" t="inlineStr"/>
       <c r="AT237" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -43092,7 +43075,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -43144,98 +43127,23 @@
       <c r="P238" t="n">
         <v>4</v>
       </c>
+      <c r="R238" t="n">
+        <v>0.003267233630263065</v>
+      </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U238" t="inlineStr">
         <is>
           <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V238" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W238" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X238" t="inlineStr">
-        <is>
-          <t>Bacterial dysentery</t>
-        </is>
-      </c>
-      <c r="Y238" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z238" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA238" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB238" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC238" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD238" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE238" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF238" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG238" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH238" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI238" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ238" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK238" t="inlineStr">
-        <is>
-          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
-        </is>
-      </c>
-      <c r="AM238" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN238" t="b">
-        <v>1</v>
       </c>
       <c r="AO238" t="inlineStr">
         <is>
@@ -43329,17 +43237,17 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -43364,7 +43272,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -43373,81 +43281,173 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>214</v>
+        <v>4</v>
       </c>
       <c r="O239" t="n">
-        <v>214</v>
-      </c>
-      <c r="R239" t="n">
-        <v>0.06131181604126484</v>
-      </c>
-      <c r="S239" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="P239" t="n">
+        <v>4</v>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V239" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W239" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X239" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y239" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z239" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB239" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC239" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD239" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE239" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF239" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG239" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH239" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI239" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ239" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK239" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM239" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN239" t="b">
+        <v>1</v>
       </c>
       <c r="AO239" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP239" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR239" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS239" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ239" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS239" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV239" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA239" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB239" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC239" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -43479,12 +43479,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -43509,7 +43509,7 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
@@ -43518,98 +43518,81 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>1</v>
+        <v>214</v>
       </c>
       <c r="O240" t="n">
-        <v>1</v>
-      </c>
-      <c r="P240" t="n">
-        <v>1</v>
+        <v>214</v>
       </c>
       <c r="R240" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.06131181604126484</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U240" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA240" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO240" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP240" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ240" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS240" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR240" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS240" t="inlineStr"/>
       <c r="AT240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV240" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA240" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB240" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC240" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -43636,7 +43619,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -43688,98 +43671,23 @@
       <c r="P241" t="n">
         <v>1</v>
       </c>
+      <c r="R241" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U241" t="inlineStr">
         <is>
           <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V241" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W241" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X241" t="inlineStr">
-        <is>
-          <t>Bacterial dysentery</t>
-        </is>
-      </c>
-      <c r="Y241" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z241" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA241" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB241" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC241" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD241" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE241" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF241" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG241" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH241" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI241" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ241" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK241" t="inlineStr">
-        <is>
-          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
-        </is>
-      </c>
-      <c r="AM241" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN241" t="b">
-        <v>1</v>
       </c>
       <c r="AO241" t="inlineStr">
         <is>
@@ -43873,17 +43781,17 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -43908,7 +43816,7 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
@@ -43917,81 +43825,173 @@
         </is>
       </c>
       <c r="N242" t="n">
-        <v>208</v>
+        <v>1</v>
       </c>
       <c r="O242" t="n">
-        <v>208</v>
-      </c>
-      <c r="R242" t="n">
-        <v>0.05959279316160321</v>
-      </c>
-      <c r="S242" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P242" t="n">
+        <v>1</v>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W242" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X242" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y242" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z242" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB242" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC242" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD242" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE242" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF242" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG242" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH242" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI242" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ242" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK242" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM242" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN242" t="b">
+        <v>1</v>
       </c>
       <c r="AO242" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP242" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR242" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS242" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ242" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS242" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU242" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV242" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA242" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB242" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC242" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -44023,12 +44023,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -44053,7 +44053,7 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
@@ -44062,98 +44062,81 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>2</v>
+        <v>208</v>
       </c>
       <c r="O243" t="n">
-        <v>2</v>
-      </c>
-      <c r="P243" t="n">
-        <v>2</v>
+        <v>208</v>
       </c>
       <c r="R243" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.05959279316160321</v>
       </c>
       <c r="S243" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U243" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA243" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO243" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP243" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ243" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS243" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR243" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS243" t="inlineStr"/>
       <c r="AT243" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU243" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV243" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA243" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB243" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC243" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -44180,7 +44163,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -44232,98 +44215,23 @@
       <c r="P244" t="n">
         <v>2</v>
       </c>
+      <c r="R244" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U244" t="inlineStr">
         <is>
           <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V244" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W244" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X244" t="inlineStr">
-        <is>
-          <t>Bacterial dysentery</t>
-        </is>
-      </c>
-      <c r="Y244" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z244" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA244" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB244" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC244" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD244" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE244" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF244" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG244" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH244" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI244" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ244" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK244" t="inlineStr">
-        <is>
-          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
-        </is>
-      </c>
-      <c r="AM244" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN244" t="b">
-        <v>1</v>
       </c>
       <c r="AO244" t="inlineStr">
         <is>
@@ -44417,17 +44325,17 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -44452,90 +44360,182 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N245" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O245" t="n">
-        <v>7</v>
-      </c>
-      <c r="R245" t="n">
-        <v>0.02570968273663853</v>
-      </c>
-      <c r="S245" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P245" t="n">
+        <v>2</v>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W245" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X245" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y245" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB245" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC245" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD245" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE245" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF245" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG245" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH245" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI245" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ245" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK245" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM245" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN245" t="b">
+        <v>1</v>
       </c>
       <c r="AO245" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP245" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR245" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS245" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ245" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS245" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU245" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV245" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA245" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB245" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC245" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -44567,12 +44567,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -44606,100 +44606,81 @@
         </is>
       </c>
       <c r="N246" t="n">
+        <v>7</v>
+      </c>
+      <c r="O246" t="n">
+        <v>7</v>
+      </c>
+      <c r="R246" t="n">
+        <v>0.02570968273663853</v>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO246" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP246" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR246" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS246" t="inlineStr"/>
+      <c r="AT246" t="n">
         <v>0</v>
       </c>
-      <c r="O246" t="n">
-        <v>0</v>
-      </c>
-      <c r="R246" t="n">
-        <v>0</v>
-      </c>
-      <c r="S246" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U246" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1210</t>
-        </is>
-      </c>
-      <c r="AA246" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO246" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP246" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ246" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR246" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS246" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1210</t>
-        </is>
-      </c>
-      <c r="AT246" t="n">
-        <v>2</v>
-      </c>
       <c r="AU246" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV246" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA246" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB246" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC246" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -44726,7 +44707,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -44775,98 +44756,23 @@
       <c r="O247" t="n">
         <v>0</v>
       </c>
+      <c r="R247" t="n">
+        <v>0</v>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U247" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1210</t>
         </is>
       </c>
-      <c r="V247" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1210</t>
-        </is>
-      </c>
-      <c r="W247" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X247" t="inlineStr">
-        <is>
-          <t>Shigella</t>
-        </is>
-      </c>
-      <c r="Y247" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z247" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA247" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB247" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC247" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD247" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE247" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF247" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG247" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH247" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI247" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ247" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK247" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1210.</t>
-        </is>
-      </c>
-      <c r="AM247" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN247" t="b">
-        <v>1</v>
       </c>
       <c r="AO247" t="inlineStr">
         <is>
@@ -44965,17 +44871,17 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -45014,76 +44920,170 @@
       <c r="O248" t="n">
         <v>0</v>
       </c>
-      <c r="R248" t="n">
-        <v>0</v>
-      </c>
-      <c r="S248" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1210</t>
+        </is>
+      </c>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1210</t>
+        </is>
+      </c>
+      <c r="W248" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X248" t="inlineStr">
+        <is>
+          <t>Shigella</t>
+        </is>
+      </c>
+      <c r="Y248" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z248" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB248" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD248" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE248" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF248" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG248" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH248" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI248" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ248" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK248" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1210.</t>
+        </is>
+      </c>
+      <c r="AM248" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN248" t="b">
+        <v>1</v>
       </c>
       <c r="AO248" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ248" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR248" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS248" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS248" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1210</t>
+        </is>
+      </c>
       <c r="AT248" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -45115,12 +45115,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -45154,100 +45154,81 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O249" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R249" t="n">
-        <v>0.07075903303182025</v>
+        <v>0</v>
       </c>
       <c r="S249" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U249" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA249" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO249" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ249" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR249" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS249" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS249" t="inlineStr"/>
       <c r="AT249" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV249" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA249" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB249" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC249" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -45274,7 +45255,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -45323,98 +45304,23 @@
       <c r="O250" t="n">
         <v>4</v>
       </c>
+      <c r="R250" t="n">
+        <v>0.07075903303182025</v>
+      </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U250" t="inlineStr">
         <is>
           <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
-      <c r="V250" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W250" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X250" t="inlineStr">
-        <is>
-          <t>Shigellose</t>
-        </is>
-      </c>
-      <c r="Y250" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z250" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA250" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB250" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC250" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD250" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE250" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF250" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG250" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH250" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI250" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ250" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK250" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM250" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN250" t="b">
-        <v>1</v>
       </c>
       <c r="AO250" t="inlineStr">
         <is>
@@ -45513,17 +45419,17 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -45548,7 +45454,7 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
@@ -45557,81 +45463,175 @@
         </is>
       </c>
       <c r="N251" t="n">
-        <v>198</v>
+        <v>4</v>
       </c>
       <c r="O251" t="n">
-        <v>198</v>
-      </c>
-      <c r="R251" t="n">
-        <v>0.05672775502883383</v>
-      </c>
-      <c r="S251" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_502_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_502_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W251" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X251" t="inlineStr">
+        <is>
+          <t>Shigellose</t>
+        </is>
+      </c>
+      <c r="Y251" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z251" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB251" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC251" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD251" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE251" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF251" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG251" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH251" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI251" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ251" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK251" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM251" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN251" t="b">
+        <v>1</v>
       </c>
       <c r="AO251" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP251" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ251" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR251" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS251" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS251" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_502_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT251" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV251" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA251" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB251" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC251" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -45663,12 +45663,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -45693,7 +45693,7 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
@@ -45702,98 +45702,81 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="O252" t="n">
-        <v>1</v>
-      </c>
-      <c r="P252" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="R252" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.05672775502883383</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U252" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA252" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO252" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ252" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS252" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR252" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS252" t="inlineStr"/>
       <c r="AT252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA252" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB252" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC252" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -45820,7 +45803,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -45872,98 +45855,23 @@
       <c r="P253" t="n">
         <v>1</v>
       </c>
+      <c r="R253" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U253" t="inlineStr">
         <is>
           <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V253" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W253" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X253" t="inlineStr">
-        <is>
-          <t>Bacterial dysentery</t>
-        </is>
-      </c>
-      <c r="Y253" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z253" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA253" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB253" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC253" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD253" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE253" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF253" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG253" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH253" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI253" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ253" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK253" t="inlineStr">
-        <is>
-          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
-        </is>
-      </c>
-      <c r="AM253" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN253" t="b">
-        <v>1</v>
       </c>
       <c r="AO253" t="inlineStr">
         <is>
@@ -46057,123 +45965,904 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N254" t="n">
+        <v>1</v>
+      </c>
+      <c r="O254" t="n">
+        <v>1</v>
+      </c>
+      <c r="P254" t="n">
+        <v>1</v>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W254" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X254" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y254" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z254" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB254" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD254" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE254" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF254" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG254" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH254" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI254" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ254" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK254" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM254" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN254" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO254" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP254" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ254" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS254" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT254" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU254" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV254" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW254" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX254" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY254" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA254" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB254" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC254" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>shigellosis</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F254" t="inlineStr">
+      <c r="F255" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G254" t="inlineStr">
+      <c r="G255" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t>D105</t>
-        </is>
-      </c>
-      <c r="I254" t="inlineStr">
-        <is>
-          <t>Shigellosis</t>
-        </is>
-      </c>
-      <c r="J254" t="inlineStr">
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
         <is>
           <t>志贺菌病</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr">
+      <c r="K255" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L254" t="inlineStr">
+      <c r="L255" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="M254" t="inlineStr">
+      <c r="M255" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N254" t="n">
+      <c r="N255" t="n">
         <v>180</v>
       </c>
-      <c r="O254" t="n">
+      <c r="O255" t="n">
         <v>180</v>
       </c>
-      <c r="R254" t="n">
+      <c r="R255" t="n">
         <v>0.05157068638984894</v>
       </c>
-      <c r="S254" t="inlineStr">
+      <c r="S255" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO254" t="inlineStr">
+      <c r="AO255" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP254" t="inlineStr">
+      <c r="AP255" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR254" t="inlineStr">
+      <c r="AR255" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS254" t="inlineStr"/>
-      <c r="AT254" t="n">
+      <c r="AS255" t="inlineStr"/>
+      <c r="AT255" t="n">
         <v>0</v>
       </c>
-      <c r="AU254" t="inlineStr">
+      <c r="AU255" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV254" t="inlineStr">
+      <c r="AV255" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW254" t="inlineStr">
+      <c r="AW255" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX254" t="inlineStr">
+      <c r="AX255" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY254" t="inlineStr">
+      <c r="AY255" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ254" t="inlineStr">
+      <c r="AZ255" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA254" t="inlineStr">
+      <c r="BA255" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB254" t="inlineStr">
+      <c r="BB255" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC254" t="inlineStr">
+      <c r="BC255" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>shigellosis</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N256" t="n">
+        <v>0</v>
+      </c>
+      <c r="O256" t="n">
+        <v>0</v>
+      </c>
+      <c r="P256" t="n">
+        <v>0</v>
+      </c>
+      <c r="R256" t="n">
+        <v>0</v>
+      </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO256" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP256" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ256" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS256" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT256" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU256" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV256" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW256" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX256" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY256" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA256" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB256" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC256" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>shigellosis</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N257" t="n">
+        <v>0</v>
+      </c>
+      <c r="O257" t="n">
+        <v>0</v>
+      </c>
+      <c r="P257" t="n">
+        <v>0</v>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W257" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X257" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y257" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z257" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB257" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC257" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD257" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE257" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF257" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG257" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH257" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI257" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ257" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK257" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM257" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN257" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO257" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP257" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ257" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS257" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT257" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU257" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV257" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW257" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX257" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY257" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA257" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB257" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC257" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>shigellosis</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N258" t="n">
+        <v>202</v>
+      </c>
+      <c r="O258" t="n">
+        <v>202</v>
+      </c>
+      <c r="R258" t="n">
+        <v>0.05787377028194158</v>
+      </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO258" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP258" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR258" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS258" t="inlineStr"/>
+      <c r="AT258" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU258" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV258" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW258" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX258" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY258" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA258" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB258" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC258" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -46212,7 +46901,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -46295,7 +46984,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10">
@@ -46305,7 +46994,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11">
@@ -46325,7 +47014,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13">
@@ -46357,7 +47046,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9484</v>
+        <v>9688</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d105/2026-2029.xlsx
+++ b/diseases/d105/2026-2029.xlsx
@@ -38459,13 +38459,13 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="O211" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="R211" t="n">
-        <v>0.7970001648357945</v>
+        <v>0.8080186002943539</v>
       </c>
       <c r="S211" t="inlineStr">
         <is>
@@ -44606,13 +44606,13 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>7</v>
+        <v>172</v>
       </c>
       <c r="O246" t="n">
-        <v>7</v>
+        <v>172</v>
       </c>
       <c r="R246" t="n">
-        <v>0.02570968273663853</v>
+        <v>0.6317236329574039</v>
       </c>
       <c r="S246" t="inlineStr">
         <is>
@@ -45154,13 +45154,13 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R249" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S249" t="inlineStr">
         <is>
@@ -46865,6 +46865,1098 @@
       <c r="BC258" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>shigellosis</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N259" t="n">
+        <v>1</v>
+      </c>
+      <c r="O259" t="n">
+        <v>1</v>
+      </c>
+      <c r="P259" t="n">
+        <v>1</v>
+      </c>
+      <c r="R259" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO259" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP259" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ259" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS259" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT259" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU259" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV259" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW259" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX259" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY259" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA259" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB259" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC259" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>shigellosis</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N260" t="n">
+        <v>1</v>
+      </c>
+      <c r="O260" t="n">
+        <v>1</v>
+      </c>
+      <c r="P260" t="n">
+        <v>1</v>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V260" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W260" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X260" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y260" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z260" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB260" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC260" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD260" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE260" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF260" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG260" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH260" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI260" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ260" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK260" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM260" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN260" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO260" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP260" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ260" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS260" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT260" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU260" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV260" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW260" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX260" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY260" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA260" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB260" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC260" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>shigellosis</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N261" t="n">
+        <v>202</v>
+      </c>
+      <c r="O261" t="n">
+        <v>202</v>
+      </c>
+      <c r="R261" t="n">
+        <v>0.05787377028194158</v>
+      </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO261" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP261" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR261" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS261" t="inlineStr"/>
+      <c r="AT261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU261" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV261" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW261" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX261" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY261" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA261" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB261" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC261" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>shigellosis</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N262" t="n">
+        <v>0</v>
+      </c>
+      <c r="O262" t="n">
+        <v>0</v>
+      </c>
+      <c r="R262" t="n">
+        <v>0</v>
+      </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1210</t>
+        </is>
+      </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO262" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP262" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ262" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR262" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS262" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1210</t>
+        </is>
+      </c>
+      <c r="AT262" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU262" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV262" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW262" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX262" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY262" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA262" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB262" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC262" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>shigellosis</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N263" t="n">
+        <v>0</v>
+      </c>
+      <c r="O263" t="n">
+        <v>0</v>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1210</t>
+        </is>
+      </c>
+      <c r="V263" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1210</t>
+        </is>
+      </c>
+      <c r="W263" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X263" t="inlineStr">
+        <is>
+          <t>Shigella</t>
+        </is>
+      </c>
+      <c r="Y263" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z263" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB263" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC263" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD263" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE263" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF263" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG263" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH263" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI263" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ263" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK263" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1210.</t>
+        </is>
+      </c>
+      <c r="AM263" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN263" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO263" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP263" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ263" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR263" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS263" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1210</t>
+        </is>
+      </c>
+      <c r="AT263" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU263" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV263" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW263" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX263" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY263" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA263" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB263" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC263" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>shigellosis</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N264" t="n">
+        <v>0</v>
+      </c>
+      <c r="O264" t="n">
+        <v>0</v>
+      </c>
+      <c r="R264" t="n">
+        <v>0</v>
+      </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO264" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP264" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR264" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS264" t="inlineStr"/>
+      <c r="AT264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU264" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV264" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW264" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX264" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY264" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA264" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB264" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC264" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -46901,7 +47993,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -46984,7 +48076,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10">
@@ -46994,7 +48086,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>257</v>
+        <v>263</v>
       </c>
     </row>
     <row r="11">
@@ -47014,7 +48106,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13">
@@ -47046,7 +48138,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9688</v>
+        <v>10060</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d105/2026-2029.xlsx
+++ b/diseases/d105/2026-2029.xlsx
@@ -44606,13 +44606,13 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="O246" t="n">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="R246" t="n">
-        <v>0.6317236329574039</v>
+        <v>0.6500876920550028</v>
       </c>
       <c r="S246" t="inlineStr">
         <is>
@@ -48138,7 +48138,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10060</v>
+        <v>10065</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d105/2026-2029.xlsx
+++ b/diseases/d105/2026-2029.xlsx
@@ -2392,7 +2392,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -7867,7 +7867,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -12795,7 +12795,7 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN68" t="b">
@@ -17720,7 +17720,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -22639,7 +22639,7 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN122" t="b">
@@ -28812,7 +28812,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -34947,7 +34947,7 @@
       </c>
       <c r="AM192" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN192" t="b">
@@ -40294,13 +40294,13 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O223" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R223" t="n">
-        <v>0.1945873408375057</v>
+        <v>0.2122770990954608</v>
       </c>
       <c r="S223" t="inlineStr">
         <is>
@@ -40458,10 +40458,10 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O224" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U224" t="inlineStr">
         <is>
@@ -40550,7 +40550,7 @@
       </c>
       <c r="AM224" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN224" t="b">
@@ -45555,7 +45555,7 @@
       </c>
       <c r="AM251" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN251" t="b">
@@ -48138,7 +48138,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10065</v>
+        <v>10066</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d105/2026-2029.xlsx
+++ b/diseases/d105/2026-2029.xlsx
@@ -52903,13 +52903,13 @@
         </is>
       </c>
       <c r="N303" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O303" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R303" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.005813909771376137</v>
       </c>
       <c r="S303" t="inlineStr">
         <is>
@@ -56286,7 +56286,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11585</v>
+        <v>11586</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d105/2026-2029.xlsx
+++ b/diseases/d105/2026-2029.xlsx
@@ -52258,13 +52258,13 @@
         </is>
       </c>
       <c r="N294" t="n">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="O294" t="n">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="R294" t="n">
-        <v>0.7125254929868393</v>
+        <v>0.752926423001557</v>
       </c>
       <c r="S294" t="inlineStr">
         <is>
@@ -57698,13 +57698,13 @@
         </is>
       </c>
       <c r="N325" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O325" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R325" t="n">
-        <v>0</v>
+        <v>0.03537951651591013</v>
       </c>
       <c r="S325" t="inlineStr">
         <is>
@@ -57862,10 +57862,10 @@
         </is>
       </c>
       <c r="N326" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O326" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U326" t="inlineStr">
         <is>
@@ -58181,6 +58181,405 @@
       <c r="BC327" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>shigellosis</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N328" t="n">
+        <v>1</v>
+      </c>
+      <c r="O328" t="n">
+        <v>1</v>
+      </c>
+      <c r="P328" t="n">
+        <v>1</v>
+      </c>
+      <c r="R328" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S328" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U328" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA328" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO328" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP328" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ328" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS328" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT328" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU328" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV328" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW328" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX328" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY328" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ328" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA328" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB328" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC328" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>shigellosis</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N329" t="n">
+        <v>1</v>
+      </c>
+      <c r="O329" t="n">
+        <v>1</v>
+      </c>
+      <c r="P329" t="n">
+        <v>1</v>
+      </c>
+      <c r="U329" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V329" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W329" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X329" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y329" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z329" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA329" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB329" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC329" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD329" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE329" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF329" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG329" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH329" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI329" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ329" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK329" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM329" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN329" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO329" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP329" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ329" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS329" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT329" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU329" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV329" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW329" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX329" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY329" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ329" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA329" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB329" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC329" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -58217,7 +58616,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -58300,7 +58699,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10">
@@ -58310,7 +58709,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="11">
@@ -58330,7 +58729,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13">
@@ -58362,7 +58761,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11871</v>
+        <v>11885</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d105/2026-2029.xlsx
+++ b/diseases/d105/2026-2029.xlsx
@@ -4707,9 +4707,6 @@
       <c r="O25" t="n">
         <v>21</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.006016580078815709</v>
       </c>
@@ -5259,9 +5256,6 @@
       <c r="O28" t="n">
         <v>139</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.03982403004549445</v>
       </c>
@@ -5811,9 +5805,6 @@
       <c r="O31" t="n">
         <v>141</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0.04039703767204833</v>
       </c>
@@ -6358,16 +6349,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O34" t="n">
-        <v>151</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="R34" t="n">
-        <v>0.04326207580481772</v>
+        <v>0.04297557199154078</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -6915,9 +6903,6 @@
       <c r="O37" t="n">
         <v>145</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0.04154305292515609</v>
       </c>
@@ -11409,9 +11394,6 @@
       <c r="O63" t="n">
         <v>144</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0.04125654911187915</v>
       </c>
@@ -11961,9 +11943,6 @@
       <c r="O66" t="n">
         <v>145</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.04154305292515609</v>
       </c>
@@ -12513,9 +12492,6 @@
       <c r="O69" t="n">
         <v>133</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0.03810500716583282</v>
       </c>
@@ -13065,9 +13041,6 @@
       <c r="O72" t="n">
         <v>152</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.04354857961809466</v>
       </c>
@@ -17568,9 +17541,6 @@
       <c r="O98" t="n">
         <v>143</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.04097004529860222</v>
       </c>
@@ -18120,9 +18090,6 @@
       <c r="O101" t="n">
         <v>152</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0.04354857961809466</v>
       </c>
@@ -18672,9 +18639,6 @@
       <c r="O104" t="n">
         <v>129</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.03695899191272507</v>
       </c>
@@ -19224,9 +19188,6 @@
       <c r="O107" t="n">
         <v>141</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.04039703767204833</v>
       </c>
@@ -23713,16 +23674,13 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O133" t="n">
-        <v>146</v>
-      </c>
-      <c r="Q133" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="R133" t="n">
-        <v>0.04182955673843303</v>
+        <v>0.04154305292515609</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -24270,9 +24228,6 @@
       <c r="O136" t="n">
         <v>134</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.03839151097910976</v>
       </c>
@@ -24822,9 +24777,6 @@
       <c r="O139" t="n">
         <v>140</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0.0401105338587714</v>
       </c>
@@ -25374,9 +25326,6 @@
       <c r="O142" t="n">
         <v>150</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.04297557199154078</v>
       </c>
@@ -29859,9 +29808,6 @@
       <c r="O168" t="n">
         <v>135</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0.0386780147923867</v>
       </c>
@@ -30411,9 +30357,6 @@
       <c r="O171" t="n">
         <v>135</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0.0386780147923867</v>
       </c>
@@ -30963,9 +30906,6 @@
       <c r="O174" t="n">
         <v>134</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0.03839151097910976</v>
       </c>
@@ -31515,9 +31455,6 @@
       <c r="O177" t="n">
         <v>37</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>0.01060064109124673</v>
       </c>
@@ -58580,6 +58517,156 @@
       <c r="BC329" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>shigellosis</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N330" t="n">
+        <v>166</v>
+      </c>
+      <c r="O330" t="n">
+        <v>166</v>
+      </c>
+      <c r="R330" t="n">
+        <v>0.0475596330039718</v>
+      </c>
+      <c r="S330" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA330" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO330" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP330" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR330" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS330" t="inlineStr"/>
+      <c r="AT330" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU330" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV330" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW330" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX330" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY330" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ330" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA330" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB330" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC330" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -58616,7 +58703,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -58699,7 +58786,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10">
@@ -58709,7 +58796,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="11">
@@ -58761,7 +58848,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11885</v>
+        <v>12049</v>
       </c>
     </row>
     <row r="16">
